--- a/templates/ERC000025/metadata_template_ERC000025.xlsx
+++ b/templates/ERC000025/metadata_template_ERC000025.xlsx
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AQ$1:$AQ$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AQ$1:$AQ$294</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
     <definedName name="observedbioticrelationship">'cv_sample'!$H$1:$H$5</definedName>
     <definedName name="oxygenationstatusofsample">'cv_sample'!$P$1:$P$2</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="relationshiptooxygen">'cv_sample'!$J$1:$J$7</definedName>
     <definedName name="sequencequalitycheck">'cv_sample'!$Z$1:$Z$3</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="805">
   <si>
     <t>alias</t>
   </si>
@@ -452,6 +452,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -542,6 +545,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1196,13 +1202,13 @@
     <t>amount or size of sample collected</t>
   </si>
   <si>
-    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: m3)</t>
+    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: kg)</t>
   </si>
   <si>
     <t>biomass</t>
   </si>
   <si>
-    <t>(Optional) Amount of biomass; should include the name for the part of biomass measured, e.g. microbial, total. can include multiple measurements (Units: t)</t>
+    <t>(Optional) Amount of biomass; should include the name for the part of biomass measured, e.g. microbial, total. can include multiple measurements (Units: kg)</t>
   </si>
   <si>
     <t>organism count</t>
@@ -1430,9 +1436,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1451,6 +1454,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1652,6 +1658,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1661,9 +1670,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1703,7 +1709,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1772,6 +1778,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1847,6 +1856,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1868,6 +1880,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1913,6 +1928,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1925,6 +1943,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1934,9 +1955,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1961,6 +1979,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2021,12 +2042,12 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
   </si>
   <si>
-    <t>Wake Island</t>
-  </si>
-  <si>
     <t>Wallis and Futuna</t>
   </si>
   <si>
@@ -2105,13 +2126,13 @@
     <t>water current</t>
   </si>
   <si>
-    <t>(Optional) Measurement of magnitude and direction of flow within a fluid (Units: m3/s)</t>
+    <t>(Optional) Measurement of magnitude and direction of flow within a fluid (Units: knot)</t>
   </si>
   <si>
     <t>pressure</t>
   </si>
   <si>
-    <t>(Optional) Pressure to which the sample is subject, in atmospheres (Units: bar)</t>
+    <t>(Optional) Pressure to which the sample is subject, in atmospheres (Units: atm)</t>
   </si>
   <si>
     <t>temperature</t>
@@ -2141,7 +2162,7 @@
     <t>calcium</t>
   </si>
   <si>
-    <t>(Optional) Concentration of calcium (Units: µmol/L)</t>
+    <t>(Optional) Concentration of calcium (Units: mg/L)</t>
   </si>
   <si>
     <t>chloride</t>
@@ -2267,13 +2288,13 @@
     <t>sulfate</t>
   </si>
   <si>
-    <t>(Optional) Concentration of sulfate (Units: µmol/L)</t>
+    <t>(Optional) Concentration of sulfate (Units: mg/L)</t>
   </si>
   <si>
     <t>sulfide</t>
   </si>
   <si>
-    <t>(Optional) Concentration of sulfide (Units: µmol/L)</t>
+    <t>(Optional) Concentration of sulfide (Units: mg/L)</t>
   </si>
   <si>
     <t>alkalinity</t>
@@ -2357,7 +2378,7 @@
     <t>sample volume or weight for DNA extraction</t>
   </si>
   <si>
-    <t>(Optional) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: ng)</t>
+    <t>(Optional) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: mL)</t>
   </si>
   <si>
     <t>nucleic acid extraction</t>
@@ -2423,7 +2444,7 @@
     <t>depth</t>
   </si>
   <si>
-    <t>(Optional) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: mm)</t>
+    <t>(Optional) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: m)</t>
   </si>
   <si>
     <t>chemical administration</t>
@@ -2956,10 +2977,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3000,10 +3021,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -3030,7 +3051,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3047,7 +3068,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -3064,7 +3085,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -3081,7 +3102,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -3098,7 +3119,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -3115,7 +3136,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -3132,7 +3153,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -3149,7 +3170,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -3166,7 +3187,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -3183,7 +3204,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -3197,7 +3218,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -3211,7 +3232,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -3225,7 +3246,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -3239,7 +3260,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -3253,7 +3274,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -3267,7 +3288,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -3281,7 +3302,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -3295,7 +3316,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -3305,8 +3326,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -3317,7 +3341,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -3328,7 +3352,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -3339,7 +3363,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3350,7 +3374,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3361,7 +3385,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3372,7 +3396,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3383,7 +3407,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3394,7 +3418,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3405,7 +3429,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3416,7 +3440,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3427,7 +3451,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3438,7 +3462,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3449,7 +3473,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3457,7 +3481,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3465,7 +3489,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3473,7 +3497,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3481,7 +3505,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3489,7 +3513,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3497,7 +3521,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3505,7 +3529,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3513,7 +3537,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3521,7 +3545,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3529,236 +3553,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3780,27 +3809,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3820,122 +3849,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3959,600 +3988,600 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
     </row>
     <row r="2" spans="1:100" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -4582,1593 +4611,1618 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:AQ289"/>
+  <dimension ref="G1:AQ294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:43">
       <c r="G1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="P1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Z1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AQ1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2" spans="7:43">
       <c r="G2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="P2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Z2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AQ2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="3" spans="7:43">
       <c r="G3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Z3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AQ3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4" spans="7:43">
       <c r="G4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AQ4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="5" spans="7:43">
       <c r="G5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AQ5" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="6" spans="7:43">
       <c r="G6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AQ6" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" spans="7:43">
       <c r="G7" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AQ7" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="8" spans="7:43">
       <c r="G8" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AQ8" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="7:43">
       <c r="G9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AQ9" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="10" spans="7:43">
       <c r="G10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AQ10" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="11" spans="7:43">
       <c r="G11" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AQ11" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="12" spans="7:43">
       <c r="G12" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AQ12" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="13" spans="7:43">
       <c r="G13" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AQ13" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="14" spans="7:43">
       <c r="G14" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AQ14" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="15" spans="7:43">
       <c r="G15" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AQ15" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="16" spans="7:43">
       <c r="G16" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AQ16" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="17" spans="7:43">
       <c r="G17" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AQ17" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="18" spans="7:43">
       <c r="G18" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AQ18" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="19" spans="7:43">
       <c r="G19" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AQ19" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="20" spans="7:43">
       <c r="G20" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AQ20" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="21" spans="7:43">
       <c r="G21" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AQ21" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="22" spans="7:43">
       <c r="G22" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AQ22" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="23" spans="7:43">
       <c r="G23" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AQ23" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="24" spans="7:43">
       <c r="G24" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AQ24" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="25" spans="7:43">
       <c r="G25" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AQ25" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="26" spans="7:43">
       <c r="G26" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AQ26" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="27" spans="7:43">
       <c r="G27" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AQ27" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="28" spans="7:43">
       <c r="G28" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AQ28" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="29" spans="7:43">
       <c r="G29" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AQ29" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="30" spans="7:43">
       <c r="G30" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AQ30" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="31" spans="7:43">
       <c r="AQ31" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="32" spans="7:43">
       <c r="AQ32" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="33" spans="43:43">
       <c r="AQ33" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="34" spans="43:43">
       <c r="AQ34" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="35" spans="43:43">
       <c r="AQ35" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="36" spans="43:43">
       <c r="AQ36" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="37" spans="43:43">
       <c r="AQ37" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="38" spans="43:43">
       <c r="AQ38" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="39" spans="43:43">
       <c r="AQ39" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="40" spans="43:43">
       <c r="AQ40" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="41" spans="43:43">
       <c r="AQ41" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="42" spans="43:43">
       <c r="AQ42" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="43" spans="43:43">
       <c r="AQ43" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="44" spans="43:43">
       <c r="AQ44" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="45" spans="43:43">
       <c r="AQ45" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="46" spans="43:43">
       <c r="AQ46" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="47" spans="43:43">
       <c r="AQ47" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="48" spans="43:43">
       <c r="AQ48" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="49" spans="43:43">
       <c r="AQ49" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="50" spans="43:43">
       <c r="AQ50" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="51" spans="43:43">
       <c r="AQ51" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="52" spans="43:43">
       <c r="AQ52" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="53" spans="43:43">
       <c r="AQ53" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="54" spans="43:43">
       <c r="AQ54" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="55" spans="43:43">
       <c r="AQ55" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="56" spans="43:43">
       <c r="AQ56" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="57" spans="43:43">
       <c r="AQ57" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="58" spans="43:43">
       <c r="AQ58" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="59" spans="43:43">
       <c r="AQ59" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="60" spans="43:43">
       <c r="AQ60" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="61" spans="43:43">
       <c r="AQ61" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="62" spans="43:43">
       <c r="AQ62" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="63" spans="43:43">
       <c r="AQ63" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="64" spans="43:43">
       <c r="AQ64" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="65" spans="43:43">
       <c r="AQ65" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="66" spans="43:43">
       <c r="AQ66" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="67" spans="43:43">
       <c r="AQ67" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="68" spans="43:43">
       <c r="AQ68" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="69" spans="43:43">
       <c r="AQ69" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="70" spans="43:43">
       <c r="AQ70" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="71" spans="43:43">
       <c r="AQ71" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="72" spans="43:43">
       <c r="AQ72" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="73" spans="43:43">
       <c r="AQ73" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="74" spans="43:43">
       <c r="AQ74" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="75" spans="43:43">
       <c r="AQ75" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="76" spans="43:43">
       <c r="AQ76" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="77" spans="43:43">
       <c r="AQ77" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="78" spans="43:43">
       <c r="AQ78" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="79" spans="43:43">
       <c r="AQ79" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="80" spans="43:43">
       <c r="AQ80" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="81" spans="43:43">
       <c r="AQ81" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="82" spans="43:43">
       <c r="AQ82" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="83" spans="43:43">
       <c r="AQ83" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="84" spans="43:43">
       <c r="AQ84" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="85" spans="43:43">
       <c r="AQ85" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="86" spans="43:43">
       <c r="AQ86" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="87" spans="43:43">
       <c r="AQ87" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="88" spans="43:43">
       <c r="AQ88" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="89" spans="43:43">
       <c r="AQ89" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="90" spans="43:43">
       <c r="AQ90" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="91" spans="43:43">
       <c r="AQ91" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="92" spans="43:43">
       <c r="AQ92" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="93" spans="43:43">
       <c r="AQ93" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="94" spans="43:43">
       <c r="AQ94" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="95" spans="43:43">
       <c r="AQ95" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="96" spans="43:43">
       <c r="AQ96" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="97" spans="43:43">
       <c r="AQ97" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="98" spans="43:43">
       <c r="AQ98" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="99" spans="43:43">
       <c r="AQ99" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="100" spans="43:43">
       <c r="AQ100" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="101" spans="43:43">
       <c r="AQ101" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="102" spans="43:43">
       <c r="AQ102" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="103" spans="43:43">
       <c r="AQ103" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="104" spans="43:43">
       <c r="AQ104" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="105" spans="43:43">
       <c r="AQ105" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="106" spans="43:43">
       <c r="AQ106" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="107" spans="43:43">
       <c r="AQ107" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="108" spans="43:43">
       <c r="AQ108" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="109" spans="43:43">
       <c r="AQ109" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="110" spans="43:43">
       <c r="AQ110" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="111" spans="43:43">
       <c r="AQ111" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="112" spans="43:43">
       <c r="AQ112" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="113" spans="43:43">
       <c r="AQ113" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="114" spans="43:43">
       <c r="AQ114" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="115" spans="43:43">
       <c r="AQ115" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="116" spans="43:43">
       <c r="AQ116" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="117" spans="43:43">
       <c r="AQ117" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="118" spans="43:43">
       <c r="AQ118" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="119" spans="43:43">
       <c r="AQ119" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="120" spans="43:43">
       <c r="AQ120" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="121" spans="43:43">
       <c r="AQ121" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="122" spans="43:43">
       <c r="AQ122" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="123" spans="43:43">
       <c r="AQ123" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="124" spans="43:43">
       <c r="AQ124" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="125" spans="43:43">
       <c r="AQ125" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="126" spans="43:43">
       <c r="AQ126" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="127" spans="43:43">
       <c r="AQ127" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="128" spans="43:43">
       <c r="AQ128" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="129" spans="43:43">
       <c r="AQ129" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="130" spans="43:43">
       <c r="AQ130" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="131" spans="43:43">
       <c r="AQ131" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="132" spans="43:43">
       <c r="AQ132" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="133" spans="43:43">
       <c r="AQ133" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="134" spans="43:43">
       <c r="AQ134" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="135" spans="43:43">
       <c r="AQ135" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="136" spans="43:43">
       <c r="AQ136" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="137" spans="43:43">
       <c r="AQ137" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="138" spans="43:43">
       <c r="AQ138" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="139" spans="43:43">
       <c r="AQ139" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="140" spans="43:43">
       <c r="AQ140" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="141" spans="43:43">
       <c r="AQ141" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="142" spans="43:43">
       <c r="AQ142" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="143" spans="43:43">
       <c r="AQ143" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="144" spans="43:43">
       <c r="AQ144" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="145" spans="43:43">
       <c r="AQ145" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="146" spans="43:43">
       <c r="AQ146" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="147" spans="43:43">
       <c r="AQ147" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="148" spans="43:43">
       <c r="AQ148" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="149" spans="43:43">
       <c r="AQ149" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="150" spans="43:43">
       <c r="AQ150" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="151" spans="43:43">
       <c r="AQ151" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="152" spans="43:43">
       <c r="AQ152" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="153" spans="43:43">
       <c r="AQ153" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="154" spans="43:43">
       <c r="AQ154" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="155" spans="43:43">
       <c r="AQ155" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="156" spans="43:43">
       <c r="AQ156" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="157" spans="43:43">
       <c r="AQ157" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="158" spans="43:43">
       <c r="AQ158" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="159" spans="43:43">
       <c r="AQ159" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="160" spans="43:43">
       <c r="AQ160" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="161" spans="43:43">
       <c r="AQ161" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="162" spans="43:43">
       <c r="AQ162" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="163" spans="43:43">
       <c r="AQ163" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="164" spans="43:43">
       <c r="AQ164" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="165" spans="43:43">
       <c r="AQ165" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="166" spans="43:43">
       <c r="AQ166" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="167" spans="43:43">
       <c r="AQ167" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="168" spans="43:43">
       <c r="AQ168" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="169" spans="43:43">
       <c r="AQ169" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="170" spans="43:43">
       <c r="AQ170" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="171" spans="43:43">
       <c r="AQ171" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="172" spans="43:43">
       <c r="AQ172" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="173" spans="43:43">
       <c r="AQ173" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="174" spans="43:43">
       <c r="AQ174" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="175" spans="43:43">
       <c r="AQ175" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="176" spans="43:43">
       <c r="AQ176" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="177" spans="43:43">
       <c r="AQ177" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="178" spans="43:43">
       <c r="AQ178" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="179" spans="43:43">
       <c r="AQ179" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="180" spans="43:43">
       <c r="AQ180" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="181" spans="43:43">
       <c r="AQ181" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="182" spans="43:43">
       <c r="AQ182" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="183" spans="43:43">
       <c r="AQ183" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="184" spans="43:43">
       <c r="AQ184" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="185" spans="43:43">
       <c r="AQ185" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="186" spans="43:43">
       <c r="AQ186" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="187" spans="43:43">
       <c r="AQ187" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="188" spans="43:43">
       <c r="AQ188" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="189" spans="43:43">
       <c r="AQ189" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="190" spans="43:43">
       <c r="AQ190" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="191" spans="43:43">
       <c r="AQ191" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="192" spans="43:43">
       <c r="AQ192" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="193" spans="43:43">
       <c r="AQ193" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="194" spans="43:43">
       <c r="AQ194" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="195" spans="43:43">
       <c r="AQ195" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="196" spans="43:43">
       <c r="AQ196" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="197" spans="43:43">
       <c r="AQ197" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="198" spans="43:43">
       <c r="AQ198" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="199" spans="43:43">
       <c r="AQ199" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="200" spans="43:43">
       <c r="AQ200" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="201" spans="43:43">
       <c r="AQ201" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="202" spans="43:43">
       <c r="AQ202" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="203" spans="43:43">
       <c r="AQ203" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="204" spans="43:43">
       <c r="AQ204" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="205" spans="43:43">
       <c r="AQ205" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="206" spans="43:43">
       <c r="AQ206" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="207" spans="43:43">
       <c r="AQ207" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="208" spans="43:43">
       <c r="AQ208" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="209" spans="43:43">
       <c r="AQ209" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="210" spans="43:43">
       <c r="AQ210" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="211" spans="43:43">
       <c r="AQ211" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="212" spans="43:43">
       <c r="AQ212" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="213" spans="43:43">
       <c r="AQ213" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="214" spans="43:43">
       <c r="AQ214" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="215" spans="43:43">
       <c r="AQ215" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="216" spans="43:43">
       <c r="AQ216" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="217" spans="43:43">
       <c r="AQ217" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="218" spans="43:43">
       <c r="AQ218" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="219" spans="43:43">
       <c r="AQ219" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="220" spans="43:43">
       <c r="AQ220" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="221" spans="43:43">
       <c r="AQ221" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="222" spans="43:43">
       <c r="AQ222" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="223" spans="43:43">
       <c r="AQ223" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="224" spans="43:43">
       <c r="AQ224" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="225" spans="43:43">
       <c r="AQ225" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="226" spans="43:43">
       <c r="AQ226" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="227" spans="43:43">
       <c r="AQ227" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="228" spans="43:43">
       <c r="AQ228" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="229" spans="43:43">
       <c r="AQ229" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="230" spans="43:43">
       <c r="AQ230" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="231" spans="43:43">
       <c r="AQ231" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="232" spans="43:43">
       <c r="AQ232" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="233" spans="43:43">
       <c r="AQ233" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="234" spans="43:43">
       <c r="AQ234" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="235" spans="43:43">
       <c r="AQ235" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="236" spans="43:43">
       <c r="AQ236" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="237" spans="43:43">
       <c r="AQ237" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="238" spans="43:43">
       <c r="AQ238" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="239" spans="43:43">
       <c r="AQ239" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="240" spans="43:43">
       <c r="AQ240" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="241" spans="43:43">
       <c r="AQ241" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="242" spans="43:43">
       <c r="AQ242" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="243" spans="43:43">
       <c r="AQ243" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="244" spans="43:43">
       <c r="AQ244" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="245" spans="43:43">
       <c r="AQ245" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="246" spans="43:43">
       <c r="AQ246" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="247" spans="43:43">
       <c r="AQ247" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="248" spans="43:43">
       <c r="AQ248" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="249" spans="43:43">
       <c r="AQ249" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="250" spans="43:43">
       <c r="AQ250" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="251" spans="43:43">
       <c r="AQ251" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="252" spans="43:43">
       <c r="AQ252" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="253" spans="43:43">
       <c r="AQ253" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="254" spans="43:43">
       <c r="AQ254" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="255" spans="43:43">
       <c r="AQ255" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="256" spans="43:43">
       <c r="AQ256" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="257" spans="43:43">
       <c r="AQ257" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="258" spans="43:43">
       <c r="AQ258" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="259" spans="43:43">
       <c r="AQ259" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="260" spans="43:43">
       <c r="AQ260" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="261" spans="43:43">
       <c r="AQ261" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="262" spans="43:43">
       <c r="AQ262" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="263" spans="43:43">
       <c r="AQ263" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="264" spans="43:43">
       <c r="AQ264" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="265" spans="43:43">
       <c r="AQ265" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="266" spans="43:43">
       <c r="AQ266" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="267" spans="43:43">
       <c r="AQ267" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="268" spans="43:43">
       <c r="AQ268" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="269" spans="43:43">
       <c r="AQ269" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="270" spans="43:43">
       <c r="AQ270" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="271" spans="43:43">
       <c r="AQ271" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="272" spans="43:43">
       <c r="AQ272" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="273" spans="43:43">
       <c r="AQ273" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="274" spans="43:43">
       <c r="AQ274" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="275" spans="43:43">
       <c r="AQ275" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="276" spans="43:43">
       <c r="AQ276" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="277" spans="43:43">
       <c r="AQ277" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="278" spans="43:43">
       <c r="AQ278" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="279" spans="43:43">
       <c r="AQ279" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="280" spans="43:43">
       <c r="AQ280" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="281" spans="43:43">
       <c r="AQ281" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="282" spans="43:43">
       <c r="AQ282" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="283" spans="43:43">
       <c r="AQ283" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="284" spans="43:43">
       <c r="AQ284" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="285" spans="43:43">
       <c r="AQ285" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="286" spans="43:43">
       <c r="AQ286" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="287" spans="43:43">
       <c r="AQ287" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="288" spans="43:43">
       <c r="AQ288" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="289" spans="43:43">
       <c r="AQ289" t="s">
-        <v>681</v>
+        <v>683</v>
+      </c>
+    </row>
+    <row r="290" spans="43:43">
+      <c r="AQ290" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="291" spans="43:43">
+      <c r="AQ291" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="292" spans="43:43">
+      <c r="AQ292" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="293" spans="43:43">
+      <c r="AQ293" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="294" spans="43:43">
+      <c r="AQ294" t="s">
+        <v>688</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000025/metadata_template_ERC000025.xlsx
+++ b/templates/ERC000025/metadata_template_ERC000025.xlsx
@@ -18,25 +18,25 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AO$1:$AO$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AP$1:$AP$294</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="observedbioticrelationship">'cv_sample'!$F$1:$F$5</definedName>
-    <definedName name="oxygenationstatusofsample">'cv_sample'!$N$1:$N$2</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
-    <definedName name="relationshiptooxygen">'cv_sample'!$H$1:$H$7</definedName>
-    <definedName name="sequencequalitycheck">'cv_sample'!$X$1:$X$3</definedName>
+    <definedName name="observedbioticrelationship">'cv_sample'!$G$1:$G$5</definedName>
+    <definedName name="oxygenationstatusofsample">'cv_sample'!$O$1:$O$2</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
+    <definedName name="relationshiptooxygen">'cv_sample'!$I$1:$I$7</definedName>
+    <definedName name="sequencequalitycheck">'cv_sample'!$Y$1:$Y$3</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
-    <definedName name="trophiclevel">'cv_sample'!$E$1:$E$30</definedName>
+    <definedName name="trophiclevel">'cv_sample'!$F$1:$F$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="803">
   <si>
     <t>alias</t>
   </si>
@@ -452,6 +452,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -542,6 +545,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -842,6 +848,12 @@
     <t>(Mandatory) Ncbi taxonomy identifier.  this is appropriate for individual organisms and some environmental samples.</t>
   </si>
   <si>
+    <t>scientific_name</t>
+  </si>
+  <si>
+    <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
     <t>sample_description</t>
   </si>
   <si>
@@ -1418,9 +1430,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1439,6 +1448,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1640,6 +1652,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1649,9 +1664,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1691,7 +1703,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1760,6 +1772,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1835,6 +1850,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1856,6 +1874,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1901,6 +1922,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1913,6 +1937,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1922,9 +1949,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1949,6 +1973,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2009,10 +2036,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -2944,10 +2971,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2988,10 +3015,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -3018,7 +3045,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3035,7 +3062,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -3052,7 +3079,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -3069,7 +3096,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -3086,7 +3113,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -3103,7 +3130,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -3120,7 +3147,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -3137,7 +3164,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -3154,7 +3181,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -3171,7 +3198,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -3185,7 +3212,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -3199,7 +3226,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -3213,7 +3240,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -3227,7 +3254,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -3241,7 +3268,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -3255,7 +3282,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -3269,7 +3296,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -3283,7 +3310,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -3293,8 +3320,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -3305,7 +3335,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -3316,7 +3346,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -3327,7 +3357,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3338,7 +3368,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3349,7 +3379,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3360,7 +3390,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3371,7 +3401,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3382,7 +3412,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3393,7 +3423,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3404,7 +3434,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3415,7 +3445,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3426,7 +3456,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3437,7 +3467,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3445,7 +3475,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3453,7 +3483,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3461,7 +3491,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3469,7 +3499,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3477,7 +3507,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3485,7 +3515,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3493,7 +3523,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3501,7 +3531,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3509,7 +3539,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3517,236 +3547,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3768,27 +3803,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3808,122 +3843,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3933,13 +3968,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CT2"/>
+  <dimension ref="A1:CU2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:98">
+    <row r="1" spans="1:99">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3947,608 +3982,614 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>300</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>332</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>678</v>
+        <v>391</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="2" spans="1:98" ht="150" customHeight="1">
+        <v>799</v>
+      </c>
+      <c r="CU1" s="1" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="2" spans="1:99" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>301</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>333</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>679</v>
+        <v>392</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>793</v>
+        <v>800</v>
+      </c>
+      <c r="CU2" s="2" t="s">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F101">
       <formula1>trophiclevel</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
       <formula1>observedbioticrelationship</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I101">
       <formula1>relationshiptooxygen</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O101">
       <formula1>oxygenationstatusofsample</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X3:X101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3:Y101">
       <formula1>sequencequalitycheck</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO3:AO101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AP3:AP101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
   </dataValidations>
@@ -4558,1593 +4599,1618 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="E1:AO289"/>
+  <dimension ref="F1:AP294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="5:41">
-      <c r="E1" t="s">
-        <v>270</v>
-      </c>
+    <row r="1" spans="6:42">
       <c r="F1" t="s">
+        <v>274</v>
+      </c>
+      <c r="G1" t="s">
+        <v>306</v>
+      </c>
+      <c r="I1" t="s">
+        <v>315</v>
+      </c>
+      <c r="O1" t="s">
+        <v>334</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>356</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="2" spans="6:42">
+      <c r="F2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G2" t="s">
+        <v>307</v>
+      </c>
+      <c r="I2" t="s">
+        <v>316</v>
+      </c>
+      <c r="O2" t="s">
+        <v>335</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>357</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="3" spans="6:42">
+      <c r="F3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G3" t="s">
+        <v>308</v>
+      </c>
+      <c r="I3" t="s">
+        <v>317</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>358</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="4" spans="6:42">
+      <c r="F4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G4" t="s">
+        <v>309</v>
+      </c>
+      <c r="I4" t="s">
+        <v>318</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="5" spans="6:42">
+      <c r="F5" t="s">
+        <v>278</v>
+      </c>
+      <c r="G5" t="s">
+        <v>310</v>
+      </c>
+      <c r="I5" t="s">
+        <v>319</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="6" spans="6:42">
+      <c r="F6" t="s">
+        <v>279</v>
+      </c>
+      <c r="I6" t="s">
+        <v>320</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="7" spans="6:42">
+      <c r="F7" t="s">
+        <v>280</v>
+      </c>
+      <c r="I7" t="s">
+        <v>321</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="8" spans="6:42">
+      <c r="F8" t="s">
+        <v>281</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="9" spans="6:42">
+      <c r="F9" t="s">
+        <v>282</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="10" spans="6:42">
+      <c r="F10" t="s">
+        <v>283</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="11" spans="6:42">
+      <c r="F11" t="s">
+        <v>284</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="12" spans="6:42">
+      <c r="F12" t="s">
+        <v>285</v>
+      </c>
+      <c r="AP12" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="13" spans="6:42">
+      <c r="F13" t="s">
+        <v>286</v>
+      </c>
+      <c r="AP13" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="14" spans="6:42">
+      <c r="F14" t="s">
+        <v>287</v>
+      </c>
+      <c r="AP14" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="15" spans="6:42">
+      <c r="F15" t="s">
+        <v>288</v>
+      </c>
+      <c r="AP15" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="16" spans="6:42">
+      <c r="F16" t="s">
+        <v>289</v>
+      </c>
+      <c r="AP16" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="17" spans="6:42">
+      <c r="F17" t="s">
+        <v>290</v>
+      </c>
+      <c r="AP17" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="18" spans="6:42">
+      <c r="F18" t="s">
+        <v>291</v>
+      </c>
+      <c r="AP18" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="19" spans="6:42">
+      <c r="F19" t="s">
+        <v>292</v>
+      </c>
+      <c r="AP19" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="20" spans="6:42">
+      <c r="F20" t="s">
+        <v>293</v>
+      </c>
+      <c r="AP20" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="21" spans="6:42">
+      <c r="F21" t="s">
+        <v>294</v>
+      </c>
+      <c r="AP21" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="22" spans="6:42">
+      <c r="F22" t="s">
+        <v>295</v>
+      </c>
+      <c r="AP22" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="23" spans="6:42">
+      <c r="F23" t="s">
+        <v>296</v>
+      </c>
+      <c r="AP23" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="24" spans="6:42">
+      <c r="F24" t="s">
+        <v>297</v>
+      </c>
+      <c r="AP24" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="25" spans="6:42">
+      <c r="F25" t="s">
+        <v>298</v>
+      </c>
+      <c r="AP25" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="26" spans="6:42">
+      <c r="F26" t="s">
+        <v>299</v>
+      </c>
+      <c r="AP26" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="27" spans="6:42">
+      <c r="F27" t="s">
+        <v>300</v>
+      </c>
+      <c r="AP27" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="28" spans="6:42">
+      <c r="F28" t="s">
+        <v>301</v>
+      </c>
+      <c r="AP28" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="29" spans="6:42">
+      <c r="F29" t="s">
         <v>302</v>
       </c>
-      <c r="H1" t="s">
-        <v>311</v>
-      </c>
-      <c r="N1" t="s">
-        <v>330</v>
-      </c>
-      <c r="X1" t="s">
-        <v>352</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="2" spans="5:41">
-      <c r="E2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="AP29" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="30" spans="6:42">
+      <c r="F30" t="s">
         <v>303</v>
       </c>
-      <c r="H2" t="s">
-        <v>312</v>
-      </c>
-      <c r="N2" t="s">
-        <v>331</v>
-      </c>
-      <c r="X2" t="s">
-        <v>353</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="3" spans="5:41">
-      <c r="E3" t="s">
-        <v>272</v>
-      </c>
-      <c r="F3" t="s">
-        <v>304</v>
-      </c>
-      <c r="H3" t="s">
-        <v>313</v>
-      </c>
-      <c r="X3" t="s">
-        <v>354</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="4" spans="5:41">
-      <c r="E4" t="s">
-        <v>273</v>
-      </c>
-      <c r="F4" t="s">
-        <v>305</v>
-      </c>
-      <c r="H4" t="s">
-        <v>314</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="5" spans="5:41">
-      <c r="E5" t="s">
-        <v>274</v>
-      </c>
-      <c r="F5" t="s">
-        <v>306</v>
-      </c>
-      <c r="H5" t="s">
-        <v>315</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="6" spans="5:41">
-      <c r="E6" t="s">
-        <v>275</v>
-      </c>
-      <c r="H6" t="s">
-        <v>316</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="7" spans="5:41">
-      <c r="E7" t="s">
-        <v>276</v>
-      </c>
-      <c r="H7" t="s">
-        <v>317</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="8" spans="5:41">
-      <c r="E8" t="s">
-        <v>277</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="9" spans="5:41">
-      <c r="E9" t="s">
-        <v>278</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="10" spans="5:41">
-      <c r="E10" t="s">
-        <v>279</v>
-      </c>
-      <c r="AO10" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="11" spans="5:41">
-      <c r="E11" t="s">
-        <v>280</v>
-      </c>
-      <c r="AO11" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="12" spans="5:41">
-      <c r="E12" t="s">
-        <v>281</v>
-      </c>
-      <c r="AO12" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="13" spans="5:41">
-      <c r="E13" t="s">
-        <v>282</v>
-      </c>
-      <c r="AO13" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="14" spans="5:41">
-      <c r="E14" t="s">
-        <v>283</v>
-      </c>
-      <c r="AO14" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="15" spans="5:41">
-      <c r="E15" t="s">
-        <v>284</v>
-      </c>
-      <c r="AO15" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="16" spans="5:41">
-      <c r="E16" t="s">
-        <v>285</v>
-      </c>
-      <c r="AO16" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="17" spans="5:41">
-      <c r="E17" t="s">
-        <v>286</v>
-      </c>
-      <c r="AO17" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="18" spans="5:41">
-      <c r="E18" t="s">
-        <v>287</v>
-      </c>
-      <c r="AO18" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="19" spans="5:41">
-      <c r="E19" t="s">
-        <v>288</v>
-      </c>
-      <c r="AO19" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="20" spans="5:41">
-      <c r="E20" t="s">
-        <v>289</v>
-      </c>
-      <c r="AO20" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="21" spans="5:41">
-      <c r="E21" t="s">
-        <v>290</v>
-      </c>
-      <c r="AO21" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="22" spans="5:41">
-      <c r="E22" t="s">
-        <v>291</v>
-      </c>
-      <c r="AO22" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="23" spans="5:41">
-      <c r="E23" t="s">
-        <v>292</v>
-      </c>
-      <c r="AO23" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="24" spans="5:41">
-      <c r="E24" t="s">
-        <v>293</v>
-      </c>
-      <c r="AO24" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="25" spans="5:41">
-      <c r="E25" t="s">
-        <v>294</v>
-      </c>
-      <c r="AO25" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="26" spans="5:41">
-      <c r="E26" t="s">
-        <v>295</v>
-      </c>
-      <c r="AO26" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="27" spans="5:41">
-      <c r="E27" t="s">
-        <v>296</v>
-      </c>
-      <c r="AO27" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="28" spans="5:41">
-      <c r="E28" t="s">
-        <v>297</v>
-      </c>
-      <c r="AO28" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="29" spans="5:41">
-      <c r="E29" t="s">
-        <v>298</v>
-      </c>
-      <c r="AO29" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="30" spans="5:41">
-      <c r="E30" t="s">
-        <v>299</v>
-      </c>
-      <c r="AO30" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="31" spans="5:41">
-      <c r="AO31" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="32" spans="5:41">
-      <c r="AO32" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="33" spans="41:41">
-      <c r="AO33" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="34" spans="41:41">
-      <c r="AO34" t="s">
+      <c r="AP30" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="35" spans="41:41">
-      <c r="AO35" t="s">
+    <row r="31" spans="6:42">
+      <c r="AP31" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="36" spans="41:41">
-      <c r="AO36" t="s">
+    <row r="32" spans="6:42">
+      <c r="AP32" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="37" spans="41:41">
-      <c r="AO37" t="s">
+    <row r="33" spans="42:42">
+      <c r="AP33" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="38" spans="41:41">
-      <c r="AO38" t="s">
+    <row r="34" spans="42:42">
+      <c r="AP34" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="39" spans="41:41">
-      <c r="AO39" t="s">
+    <row r="35" spans="42:42">
+      <c r="AP35" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="40" spans="41:41">
-      <c r="AO40" t="s">
+    <row r="36" spans="42:42">
+      <c r="AP36" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="41" spans="41:41">
-      <c r="AO41" t="s">
+    <row r="37" spans="42:42">
+      <c r="AP37" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="42" spans="41:41">
-      <c r="AO42" t="s">
+    <row r="38" spans="42:42">
+      <c r="AP38" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="43" spans="41:41">
-      <c r="AO43" t="s">
+    <row r="39" spans="42:42">
+      <c r="AP39" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="44" spans="41:41">
-      <c r="AO44" t="s">
+    <row r="40" spans="42:42">
+      <c r="AP40" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="45" spans="41:41">
-      <c r="AO45" t="s">
+    <row r="41" spans="42:42">
+      <c r="AP41" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="46" spans="41:41">
-      <c r="AO46" t="s">
+    <row r="42" spans="42:42">
+      <c r="AP42" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="47" spans="41:41">
-      <c r="AO47" t="s">
+    <row r="43" spans="42:42">
+      <c r="AP43" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="48" spans="41:41">
-      <c r="AO48" t="s">
+    <row r="44" spans="42:42">
+      <c r="AP44" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="49" spans="41:41">
-      <c r="AO49" t="s">
+    <row r="45" spans="42:42">
+      <c r="AP45" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="50" spans="41:41">
-      <c r="AO50" t="s">
+    <row r="46" spans="42:42">
+      <c r="AP46" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="51" spans="41:41">
-      <c r="AO51" t="s">
+    <row r="47" spans="42:42">
+      <c r="AP47" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="52" spans="41:41">
-      <c r="AO52" t="s">
+    <row r="48" spans="42:42">
+      <c r="AP48" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="53" spans="41:41">
-      <c r="AO53" t="s">
+    <row r="49" spans="42:42">
+      <c r="AP49" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="54" spans="41:41">
-      <c r="AO54" t="s">
+    <row r="50" spans="42:42">
+      <c r="AP50" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="55" spans="41:41">
-      <c r="AO55" t="s">
+    <row r="51" spans="42:42">
+      <c r="AP51" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="56" spans="41:41">
-      <c r="AO56" t="s">
+    <row r="52" spans="42:42">
+      <c r="AP52" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="57" spans="41:41">
-      <c r="AO57" t="s">
+    <row r="53" spans="42:42">
+      <c r="AP53" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="58" spans="41:41">
-      <c r="AO58" t="s">
+    <row r="54" spans="42:42">
+      <c r="AP54" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="59" spans="41:41">
-      <c r="AO59" t="s">
+    <row r="55" spans="42:42">
+      <c r="AP55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="60" spans="41:41">
-      <c r="AO60" t="s">
+    <row r="56" spans="42:42">
+      <c r="AP56" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="61" spans="41:41">
-      <c r="AO61" t="s">
+    <row r="57" spans="42:42">
+      <c r="AP57" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="62" spans="41:41">
-      <c r="AO62" t="s">
+    <row r="58" spans="42:42">
+      <c r="AP58" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="63" spans="41:41">
-      <c r="AO63" t="s">
+    <row r="59" spans="42:42">
+      <c r="AP59" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="64" spans="41:41">
-      <c r="AO64" t="s">
+    <row r="60" spans="42:42">
+      <c r="AP60" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="65" spans="41:41">
-      <c r="AO65" t="s">
+    <row r="61" spans="42:42">
+      <c r="AP61" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="66" spans="41:41">
-      <c r="AO66" t="s">
+    <row r="62" spans="42:42">
+      <c r="AP62" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="67" spans="41:41">
-      <c r="AO67" t="s">
+    <row r="63" spans="42:42">
+      <c r="AP63" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="68" spans="41:41">
-      <c r="AO68" t="s">
+    <row r="64" spans="42:42">
+      <c r="AP64" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="69" spans="41:41">
-      <c r="AO69" t="s">
+    <row r="65" spans="42:42">
+      <c r="AP65" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="70" spans="41:41">
-      <c r="AO70" t="s">
+    <row r="66" spans="42:42">
+      <c r="AP66" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="71" spans="41:41">
-      <c r="AO71" t="s">
+    <row r="67" spans="42:42">
+      <c r="AP67" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="72" spans="41:41">
-      <c r="AO72" t="s">
+    <row r="68" spans="42:42">
+      <c r="AP68" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="73" spans="41:41">
-      <c r="AO73" t="s">
+    <row r="69" spans="42:42">
+      <c r="AP69" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="74" spans="41:41">
-      <c r="AO74" t="s">
+    <row r="70" spans="42:42">
+      <c r="AP70" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="75" spans="41:41">
-      <c r="AO75" t="s">
+    <row r="71" spans="42:42">
+      <c r="AP71" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="76" spans="41:41">
-      <c r="AO76" t="s">
+    <row r="72" spans="42:42">
+      <c r="AP72" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="77" spans="41:41">
-      <c r="AO77" t="s">
+    <row r="73" spans="42:42">
+      <c r="AP73" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="78" spans="41:41">
-      <c r="AO78" t="s">
+    <row r="74" spans="42:42">
+      <c r="AP74" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="79" spans="41:41">
-      <c r="AO79" t="s">
+    <row r="75" spans="42:42">
+      <c r="AP75" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="80" spans="41:41">
-      <c r="AO80" t="s">
+    <row r="76" spans="42:42">
+      <c r="AP76" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="81" spans="41:41">
-      <c r="AO81" t="s">
+    <row r="77" spans="42:42">
+      <c r="AP77" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="82" spans="41:41">
-      <c r="AO82" t="s">
+    <row r="78" spans="42:42">
+      <c r="AP78" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="83" spans="41:41">
-      <c r="AO83" t="s">
+    <row r="79" spans="42:42">
+      <c r="AP79" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="84" spans="41:41">
-      <c r="AO84" t="s">
+    <row r="80" spans="42:42">
+      <c r="AP80" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="85" spans="41:41">
-      <c r="AO85" t="s">
+    <row r="81" spans="42:42">
+      <c r="AP81" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="86" spans="41:41">
-      <c r="AO86" t="s">
+    <row r="82" spans="42:42">
+      <c r="AP82" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="87" spans="41:41">
-      <c r="AO87" t="s">
+    <row r="83" spans="42:42">
+      <c r="AP83" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="88" spans="41:41">
-      <c r="AO88" t="s">
+    <row r="84" spans="42:42">
+      <c r="AP84" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="89" spans="41:41">
-      <c r="AO89" t="s">
+    <row r="85" spans="42:42">
+      <c r="AP85" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="90" spans="41:41">
-      <c r="AO90" t="s">
+    <row r="86" spans="42:42">
+      <c r="AP86" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="91" spans="41:41">
-      <c r="AO91" t="s">
+    <row r="87" spans="42:42">
+      <c r="AP87" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="92" spans="41:41">
-      <c r="AO92" t="s">
+    <row r="88" spans="42:42">
+      <c r="AP88" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="93" spans="41:41">
-      <c r="AO93" t="s">
+    <row r="89" spans="42:42">
+      <c r="AP89" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="94" spans="41:41">
-      <c r="AO94" t="s">
+    <row r="90" spans="42:42">
+      <c r="AP90" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="95" spans="41:41">
-      <c r="AO95" t="s">
+    <row r="91" spans="42:42">
+      <c r="AP91" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="96" spans="41:41">
-      <c r="AO96" t="s">
+    <row r="92" spans="42:42">
+      <c r="AP92" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="97" spans="41:41">
-      <c r="AO97" t="s">
+    <row r="93" spans="42:42">
+      <c r="AP93" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="98" spans="41:41">
-      <c r="AO98" t="s">
+    <row r="94" spans="42:42">
+      <c r="AP94" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="99" spans="41:41">
-      <c r="AO99" t="s">
+    <row r="95" spans="42:42">
+      <c r="AP95" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="100" spans="41:41">
-      <c r="AO100" t="s">
+    <row r="96" spans="42:42">
+      <c r="AP96" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="101" spans="41:41">
-      <c r="AO101" t="s">
+    <row r="97" spans="42:42">
+      <c r="AP97" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="102" spans="41:41">
-      <c r="AO102" t="s">
+    <row r="98" spans="42:42">
+      <c r="AP98" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="103" spans="41:41">
-      <c r="AO103" t="s">
+    <row r="99" spans="42:42">
+      <c r="AP99" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="104" spans="41:41">
-      <c r="AO104" t="s">
+    <row r="100" spans="42:42">
+      <c r="AP100" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="105" spans="41:41">
-      <c r="AO105" t="s">
+    <row r="101" spans="42:42">
+      <c r="AP101" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="106" spans="41:41">
-      <c r="AO106" t="s">
+    <row r="102" spans="42:42">
+      <c r="AP102" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="107" spans="41:41">
-      <c r="AO107" t="s">
+    <row r="103" spans="42:42">
+      <c r="AP103" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="108" spans="41:41">
-      <c r="AO108" t="s">
+    <row r="104" spans="42:42">
+      <c r="AP104" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="109" spans="41:41">
-      <c r="AO109" t="s">
+    <row r="105" spans="42:42">
+      <c r="AP105" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="110" spans="41:41">
-      <c r="AO110" t="s">
+    <row r="106" spans="42:42">
+      <c r="AP106" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="111" spans="41:41">
-      <c r="AO111" t="s">
+    <row r="107" spans="42:42">
+      <c r="AP107" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="112" spans="41:41">
-      <c r="AO112" t="s">
+    <row r="108" spans="42:42">
+      <c r="AP108" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="113" spans="41:41">
-      <c r="AO113" t="s">
+    <row r="109" spans="42:42">
+      <c r="AP109" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="114" spans="41:41">
-      <c r="AO114" t="s">
+    <row r="110" spans="42:42">
+      <c r="AP110" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="115" spans="41:41">
-      <c r="AO115" t="s">
+    <row r="111" spans="42:42">
+      <c r="AP111" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="116" spans="41:41">
-      <c r="AO116" t="s">
+    <row r="112" spans="42:42">
+      <c r="AP112" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="117" spans="41:41">
-      <c r="AO117" t="s">
+    <row r="113" spans="42:42">
+      <c r="AP113" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="118" spans="41:41">
-      <c r="AO118" t="s">
+    <row r="114" spans="42:42">
+      <c r="AP114" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="119" spans="41:41">
-      <c r="AO119" t="s">
+    <row r="115" spans="42:42">
+      <c r="AP115" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="120" spans="41:41">
-      <c r="AO120" t="s">
+    <row r="116" spans="42:42">
+      <c r="AP116" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="121" spans="41:41">
-      <c r="AO121" t="s">
+    <row r="117" spans="42:42">
+      <c r="AP117" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="122" spans="41:41">
-      <c r="AO122" t="s">
+    <row r="118" spans="42:42">
+      <c r="AP118" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="123" spans="41:41">
-      <c r="AO123" t="s">
+    <row r="119" spans="42:42">
+      <c r="AP119" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="124" spans="41:41">
-      <c r="AO124" t="s">
+    <row r="120" spans="42:42">
+      <c r="AP120" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="125" spans="41:41">
-      <c r="AO125" t="s">
+    <row r="121" spans="42:42">
+      <c r="AP121" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="126" spans="41:41">
-      <c r="AO126" t="s">
+    <row r="122" spans="42:42">
+      <c r="AP122" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="127" spans="41:41">
-      <c r="AO127" t="s">
+    <row r="123" spans="42:42">
+      <c r="AP123" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="128" spans="41:41">
-      <c r="AO128" t="s">
+    <row r="124" spans="42:42">
+      <c r="AP124" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="129" spans="41:41">
-      <c r="AO129" t="s">
+    <row r="125" spans="42:42">
+      <c r="AP125" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="130" spans="41:41">
-      <c r="AO130" t="s">
+    <row r="126" spans="42:42">
+      <c r="AP126" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="131" spans="41:41">
-      <c r="AO131" t="s">
+    <row r="127" spans="42:42">
+      <c r="AP127" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="132" spans="41:41">
-      <c r="AO132" t="s">
+    <row r="128" spans="42:42">
+      <c r="AP128" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="133" spans="41:41">
-      <c r="AO133" t="s">
+    <row r="129" spans="42:42">
+      <c r="AP129" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="134" spans="41:41">
-      <c r="AO134" t="s">
+    <row r="130" spans="42:42">
+      <c r="AP130" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="135" spans="41:41">
-      <c r="AO135" t="s">
+    <row r="131" spans="42:42">
+      <c r="AP131" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="136" spans="41:41">
-      <c r="AO136" t="s">
+    <row r="132" spans="42:42">
+      <c r="AP132" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="137" spans="41:41">
-      <c r="AO137" t="s">
+    <row r="133" spans="42:42">
+      <c r="AP133" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="138" spans="41:41">
-      <c r="AO138" t="s">
+    <row r="134" spans="42:42">
+      <c r="AP134" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="139" spans="41:41">
-      <c r="AO139" t="s">
+    <row r="135" spans="42:42">
+      <c r="AP135" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="140" spans="41:41">
-      <c r="AO140" t="s">
+    <row r="136" spans="42:42">
+      <c r="AP136" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="141" spans="41:41">
-      <c r="AO141" t="s">
+    <row r="137" spans="42:42">
+      <c r="AP137" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="142" spans="41:41">
-      <c r="AO142" t="s">
+    <row r="138" spans="42:42">
+      <c r="AP138" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="143" spans="41:41">
-      <c r="AO143" t="s">
+    <row r="139" spans="42:42">
+      <c r="AP139" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="144" spans="41:41">
-      <c r="AO144" t="s">
+    <row r="140" spans="42:42">
+      <c r="AP140" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="145" spans="41:41">
-      <c r="AO145" t="s">
+    <row r="141" spans="42:42">
+      <c r="AP141" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="146" spans="41:41">
-      <c r="AO146" t="s">
+    <row r="142" spans="42:42">
+      <c r="AP142" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="147" spans="41:41">
-      <c r="AO147" t="s">
+    <row r="143" spans="42:42">
+      <c r="AP143" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="148" spans="41:41">
-      <c r="AO148" t="s">
+    <row r="144" spans="42:42">
+      <c r="AP144" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="149" spans="41:41">
-      <c r="AO149" t="s">
+    <row r="145" spans="42:42">
+      <c r="AP145" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="150" spans="41:41">
-      <c r="AO150" t="s">
+    <row r="146" spans="42:42">
+      <c r="AP146" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="151" spans="41:41">
-      <c r="AO151" t="s">
+    <row r="147" spans="42:42">
+      <c r="AP147" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="152" spans="41:41">
-      <c r="AO152" t="s">
+    <row r="148" spans="42:42">
+      <c r="AP148" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="153" spans="41:41">
-      <c r="AO153" t="s">
+    <row r="149" spans="42:42">
+      <c r="AP149" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="154" spans="41:41">
-      <c r="AO154" t="s">
+    <row r="150" spans="42:42">
+      <c r="AP150" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="155" spans="41:41">
-      <c r="AO155" t="s">
+    <row r="151" spans="42:42">
+      <c r="AP151" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="156" spans="41:41">
-      <c r="AO156" t="s">
+    <row r="152" spans="42:42">
+      <c r="AP152" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="157" spans="41:41">
-      <c r="AO157" t="s">
+    <row r="153" spans="42:42">
+      <c r="AP153" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="158" spans="41:41">
-      <c r="AO158" t="s">
+    <row r="154" spans="42:42">
+      <c r="AP154" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="159" spans="41:41">
-      <c r="AO159" t="s">
+    <row r="155" spans="42:42">
+      <c r="AP155" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="160" spans="41:41">
-      <c r="AO160" t="s">
+    <row r="156" spans="42:42">
+      <c r="AP156" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="161" spans="41:41">
-      <c r="AO161" t="s">
+    <row r="157" spans="42:42">
+      <c r="AP157" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="162" spans="41:41">
-      <c r="AO162" t="s">
+    <row r="158" spans="42:42">
+      <c r="AP158" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="163" spans="41:41">
-      <c r="AO163" t="s">
+    <row r="159" spans="42:42">
+      <c r="AP159" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="164" spans="41:41">
-      <c r="AO164" t="s">
+    <row r="160" spans="42:42">
+      <c r="AP160" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="165" spans="41:41">
-      <c r="AO165" t="s">
+    <row r="161" spans="42:42">
+      <c r="AP161" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="166" spans="41:41">
-      <c r="AO166" t="s">
+    <row r="162" spans="42:42">
+      <c r="AP162" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="167" spans="41:41">
-      <c r="AO167" t="s">
+    <row r="163" spans="42:42">
+      <c r="AP163" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="168" spans="41:41">
-      <c r="AO168" t="s">
+    <row r="164" spans="42:42">
+      <c r="AP164" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="169" spans="41:41">
-      <c r="AO169" t="s">
+    <row r="165" spans="42:42">
+      <c r="AP165" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="170" spans="41:41">
-      <c r="AO170" t="s">
+    <row r="166" spans="42:42">
+      <c r="AP166" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="171" spans="41:41">
-      <c r="AO171" t="s">
+    <row r="167" spans="42:42">
+      <c r="AP167" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="172" spans="41:41">
-      <c r="AO172" t="s">
+    <row r="168" spans="42:42">
+      <c r="AP168" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="173" spans="41:41">
-      <c r="AO173" t="s">
+    <row r="169" spans="42:42">
+      <c r="AP169" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="174" spans="41:41">
-      <c r="AO174" t="s">
+    <row r="170" spans="42:42">
+      <c r="AP170" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="175" spans="41:41">
-      <c r="AO175" t="s">
+    <row r="171" spans="42:42">
+      <c r="AP171" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="176" spans="41:41">
-      <c r="AO176" t="s">
+    <row r="172" spans="42:42">
+      <c r="AP172" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="177" spans="41:41">
-      <c r="AO177" t="s">
+    <row r="173" spans="42:42">
+      <c r="AP173" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="178" spans="41:41">
-      <c r="AO178" t="s">
+    <row r="174" spans="42:42">
+      <c r="AP174" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="179" spans="41:41">
-      <c r="AO179" t="s">
+    <row r="175" spans="42:42">
+      <c r="AP175" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="180" spans="41:41">
-      <c r="AO180" t="s">
+    <row r="176" spans="42:42">
+      <c r="AP176" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="181" spans="41:41">
-      <c r="AO181" t="s">
+    <row r="177" spans="42:42">
+      <c r="AP177" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="182" spans="41:41">
-      <c r="AO182" t="s">
+    <row r="178" spans="42:42">
+      <c r="AP178" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="183" spans="41:41">
-      <c r="AO183" t="s">
+    <row r="179" spans="42:42">
+      <c r="AP179" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="184" spans="41:41">
-      <c r="AO184" t="s">
+    <row r="180" spans="42:42">
+      <c r="AP180" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="185" spans="41:41">
-      <c r="AO185" t="s">
+    <row r="181" spans="42:42">
+      <c r="AP181" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="186" spans="41:41">
-      <c r="AO186" t="s">
+    <row r="182" spans="42:42">
+      <c r="AP182" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="187" spans="41:41">
-      <c r="AO187" t="s">
+    <row r="183" spans="42:42">
+      <c r="AP183" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="188" spans="41:41">
-      <c r="AO188" t="s">
+    <row r="184" spans="42:42">
+      <c r="AP184" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="189" spans="41:41">
-      <c r="AO189" t="s">
+    <row r="185" spans="42:42">
+      <c r="AP185" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="190" spans="41:41">
-      <c r="AO190" t="s">
+    <row r="186" spans="42:42">
+      <c r="AP186" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="191" spans="41:41">
-      <c r="AO191" t="s">
+    <row r="187" spans="42:42">
+      <c r="AP187" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="192" spans="41:41">
-      <c r="AO192" t="s">
+    <row r="188" spans="42:42">
+      <c r="AP188" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="193" spans="41:41">
-      <c r="AO193" t="s">
+    <row r="189" spans="42:42">
+      <c r="AP189" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="194" spans="41:41">
-      <c r="AO194" t="s">
+    <row r="190" spans="42:42">
+      <c r="AP190" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="195" spans="41:41">
-      <c r="AO195" t="s">
+    <row r="191" spans="42:42">
+      <c r="AP191" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="196" spans="41:41">
-      <c r="AO196" t="s">
+    <row r="192" spans="42:42">
+      <c r="AP192" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="197" spans="41:41">
-      <c r="AO197" t="s">
+    <row r="193" spans="42:42">
+      <c r="AP193" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="198" spans="41:41">
-      <c r="AO198" t="s">
+    <row r="194" spans="42:42">
+      <c r="AP194" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="199" spans="41:41">
-      <c r="AO199" t="s">
+    <row r="195" spans="42:42">
+      <c r="AP195" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="200" spans="41:41">
-      <c r="AO200" t="s">
+    <row r="196" spans="42:42">
+      <c r="AP196" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="201" spans="41:41">
-      <c r="AO201" t="s">
+    <row r="197" spans="42:42">
+      <c r="AP197" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="202" spans="41:41">
-      <c r="AO202" t="s">
+    <row r="198" spans="42:42">
+      <c r="AP198" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="203" spans="41:41">
-      <c r="AO203" t="s">
+    <row r="199" spans="42:42">
+      <c r="AP199" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="204" spans="41:41">
-      <c r="AO204" t="s">
+    <row r="200" spans="42:42">
+      <c r="AP200" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="205" spans="41:41">
-      <c r="AO205" t="s">
+    <row r="201" spans="42:42">
+      <c r="AP201" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="206" spans="41:41">
-      <c r="AO206" t="s">
+    <row r="202" spans="42:42">
+      <c r="AP202" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="207" spans="41:41">
-      <c r="AO207" t="s">
+    <row r="203" spans="42:42">
+      <c r="AP203" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="208" spans="41:41">
-      <c r="AO208" t="s">
+    <row r="204" spans="42:42">
+      <c r="AP204" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="209" spans="41:41">
-      <c r="AO209" t="s">
+    <row r="205" spans="42:42">
+      <c r="AP205" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="210" spans="41:41">
-      <c r="AO210" t="s">
+    <row r="206" spans="42:42">
+      <c r="AP206" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="211" spans="41:41">
-      <c r="AO211" t="s">
+    <row r="207" spans="42:42">
+      <c r="AP207" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="212" spans="41:41">
-      <c r="AO212" t="s">
+    <row r="208" spans="42:42">
+      <c r="AP208" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="213" spans="41:41">
-      <c r="AO213" t="s">
+    <row r="209" spans="42:42">
+      <c r="AP209" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="214" spans="41:41">
-      <c r="AO214" t="s">
+    <row r="210" spans="42:42">
+      <c r="AP210" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="215" spans="41:41">
-      <c r="AO215" t="s">
+    <row r="211" spans="42:42">
+      <c r="AP211" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="216" spans="41:41">
-      <c r="AO216" t="s">
+    <row r="212" spans="42:42">
+      <c r="AP212" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="217" spans="41:41">
-      <c r="AO217" t="s">
+    <row r="213" spans="42:42">
+      <c r="AP213" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="218" spans="41:41">
-      <c r="AO218" t="s">
+    <row r="214" spans="42:42">
+      <c r="AP214" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="219" spans="41:41">
-      <c r="AO219" t="s">
+    <row r="215" spans="42:42">
+      <c r="AP215" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="220" spans="41:41">
-      <c r="AO220" t="s">
+    <row r="216" spans="42:42">
+      <c r="AP216" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="221" spans="41:41">
-      <c r="AO221" t="s">
+    <row r="217" spans="42:42">
+      <c r="AP217" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="222" spans="41:41">
-      <c r="AO222" t="s">
+    <row r="218" spans="42:42">
+      <c r="AP218" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="223" spans="41:41">
-      <c r="AO223" t="s">
+    <row r="219" spans="42:42">
+      <c r="AP219" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="224" spans="41:41">
-      <c r="AO224" t="s">
+    <row r="220" spans="42:42">
+      <c r="AP220" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="225" spans="41:41">
-      <c r="AO225" t="s">
+    <row r="221" spans="42:42">
+      <c r="AP221" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="226" spans="41:41">
-      <c r="AO226" t="s">
+    <row r="222" spans="42:42">
+      <c r="AP222" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="227" spans="41:41">
-      <c r="AO227" t="s">
+    <row r="223" spans="42:42">
+      <c r="AP223" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="228" spans="41:41">
-      <c r="AO228" t="s">
+    <row r="224" spans="42:42">
+      <c r="AP224" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="229" spans="41:41">
-      <c r="AO229" t="s">
+    <row r="225" spans="42:42">
+      <c r="AP225" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="230" spans="41:41">
-      <c r="AO230" t="s">
+    <row r="226" spans="42:42">
+      <c r="AP226" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="231" spans="41:41">
-      <c r="AO231" t="s">
+    <row r="227" spans="42:42">
+      <c r="AP227" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="232" spans="41:41">
-      <c r="AO232" t="s">
+    <row r="228" spans="42:42">
+      <c r="AP228" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="233" spans="41:41">
-      <c r="AO233" t="s">
+    <row r="229" spans="42:42">
+      <c r="AP229" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="234" spans="41:41">
-      <c r="AO234" t="s">
+    <row r="230" spans="42:42">
+      <c r="AP230" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="235" spans="41:41">
-      <c r="AO235" t="s">
+    <row r="231" spans="42:42">
+      <c r="AP231" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="236" spans="41:41">
-      <c r="AO236" t="s">
+    <row r="232" spans="42:42">
+      <c r="AP232" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="237" spans="41:41">
-      <c r="AO237" t="s">
+    <row r="233" spans="42:42">
+      <c r="AP233" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="238" spans="41:41">
-      <c r="AO238" t="s">
+    <row r="234" spans="42:42">
+      <c r="AP234" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="239" spans="41:41">
-      <c r="AO239" t="s">
+    <row r="235" spans="42:42">
+      <c r="AP235" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="240" spans="41:41">
-      <c r="AO240" t="s">
+    <row r="236" spans="42:42">
+      <c r="AP236" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="241" spans="41:41">
-      <c r="AO241" t="s">
+    <row r="237" spans="42:42">
+      <c r="AP237" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="242" spans="41:41">
-      <c r="AO242" t="s">
+    <row r="238" spans="42:42">
+      <c r="AP238" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="243" spans="41:41">
-      <c r="AO243" t="s">
+    <row r="239" spans="42:42">
+      <c r="AP239" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="244" spans="41:41">
-      <c r="AO244" t="s">
+    <row r="240" spans="42:42">
+      <c r="AP240" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="245" spans="41:41">
-      <c r="AO245" t="s">
+    <row r="241" spans="42:42">
+      <c r="AP241" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="246" spans="41:41">
-      <c r="AO246" t="s">
+    <row r="242" spans="42:42">
+      <c r="AP242" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="247" spans="41:41">
-      <c r="AO247" t="s">
+    <row r="243" spans="42:42">
+      <c r="AP243" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="248" spans="41:41">
-      <c r="AO248" t="s">
+    <row r="244" spans="42:42">
+      <c r="AP244" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="249" spans="41:41">
-      <c r="AO249" t="s">
+    <row r="245" spans="42:42">
+      <c r="AP245" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="250" spans="41:41">
-      <c r="AO250" t="s">
+    <row r="246" spans="42:42">
+      <c r="AP246" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="251" spans="41:41">
-      <c r="AO251" t="s">
+    <row r="247" spans="42:42">
+      <c r="AP247" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="252" spans="41:41">
-      <c r="AO252" t="s">
+    <row r="248" spans="42:42">
+      <c r="AP248" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="253" spans="41:41">
-      <c r="AO253" t="s">
+    <row r="249" spans="42:42">
+      <c r="AP249" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="254" spans="41:41">
-      <c r="AO254" t="s">
+    <row r="250" spans="42:42">
+      <c r="AP250" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="255" spans="41:41">
-      <c r="AO255" t="s">
+    <row r="251" spans="42:42">
+      <c r="AP251" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="256" spans="41:41">
-      <c r="AO256" t="s">
+    <row r="252" spans="42:42">
+      <c r="AP252" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="257" spans="41:41">
-      <c r="AO257" t="s">
+    <row r="253" spans="42:42">
+      <c r="AP253" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="258" spans="41:41">
-      <c r="AO258" t="s">
+    <row r="254" spans="42:42">
+      <c r="AP254" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="259" spans="41:41">
-      <c r="AO259" t="s">
+    <row r="255" spans="42:42">
+      <c r="AP255" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="260" spans="41:41">
-      <c r="AO260" t="s">
+    <row r="256" spans="42:42">
+      <c r="AP256" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="261" spans="41:41">
-      <c r="AO261" t="s">
+    <row r="257" spans="42:42">
+      <c r="AP257" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="262" spans="41:41">
-      <c r="AO262" t="s">
+    <row r="258" spans="42:42">
+      <c r="AP258" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="263" spans="41:41">
-      <c r="AO263" t="s">
+    <row r="259" spans="42:42">
+      <c r="AP259" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="264" spans="41:41">
-      <c r="AO264" t="s">
+    <row r="260" spans="42:42">
+      <c r="AP260" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="265" spans="41:41">
-      <c r="AO265" t="s">
+    <row r="261" spans="42:42">
+      <c r="AP261" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="266" spans="41:41">
-      <c r="AO266" t="s">
+    <row r="262" spans="42:42">
+      <c r="AP262" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="267" spans="41:41">
-      <c r="AO267" t="s">
+    <row r="263" spans="42:42">
+      <c r="AP263" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="268" spans="41:41">
-      <c r="AO268" t="s">
+    <row r="264" spans="42:42">
+      <c r="AP264" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="269" spans="41:41">
-      <c r="AO269" t="s">
+    <row r="265" spans="42:42">
+      <c r="AP265" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="270" spans="41:41">
-      <c r="AO270" t="s">
+    <row r="266" spans="42:42">
+      <c r="AP266" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="271" spans="41:41">
-      <c r="AO271" t="s">
+    <row r="267" spans="42:42">
+      <c r="AP267" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="272" spans="41:41">
-      <c r="AO272" t="s">
+    <row r="268" spans="42:42">
+      <c r="AP268" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="273" spans="41:41">
-      <c r="AO273" t="s">
+    <row r="269" spans="42:42">
+      <c r="AP269" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="274" spans="41:41">
-      <c r="AO274" t="s">
+    <row r="270" spans="42:42">
+      <c r="AP270" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="275" spans="41:41">
-      <c r="AO275" t="s">
+    <row r="271" spans="42:42">
+      <c r="AP271" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="276" spans="41:41">
-      <c r="AO276" t="s">
+    <row r="272" spans="42:42">
+      <c r="AP272" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="277" spans="41:41">
-      <c r="AO277" t="s">
+    <row r="273" spans="42:42">
+      <c r="AP273" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="278" spans="41:41">
-      <c r="AO278" t="s">
+    <row r="274" spans="42:42">
+      <c r="AP274" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="279" spans="41:41">
-      <c r="AO279" t="s">
+    <row r="275" spans="42:42">
+      <c r="AP275" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="280" spans="41:41">
-      <c r="AO280" t="s">
+    <row r="276" spans="42:42">
+      <c r="AP276" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="281" spans="41:41">
-      <c r="AO281" t="s">
+    <row r="277" spans="42:42">
+      <c r="AP277" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="282" spans="41:41">
-      <c r="AO282" t="s">
+    <row r="278" spans="42:42">
+      <c r="AP278" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="283" spans="41:41">
-      <c r="AO283" t="s">
+    <row r="279" spans="42:42">
+      <c r="AP279" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="284" spans="41:41">
-      <c r="AO284" t="s">
+    <row r="280" spans="42:42">
+      <c r="AP280" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="285" spans="41:41">
-      <c r="AO285" t="s">
+    <row r="281" spans="42:42">
+      <c r="AP281" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="286" spans="41:41">
-      <c r="AO286" t="s">
+    <row r="282" spans="42:42">
+      <c r="AP282" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="287" spans="41:41">
-      <c r="AO287" t="s">
+    <row r="283" spans="42:42">
+      <c r="AP283" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="288" spans="41:41">
-      <c r="AO288" t="s">
+    <row r="284" spans="42:42">
+      <c r="AP284" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="289" spans="41:41">
-      <c r="AO289" t="s">
+    <row r="285" spans="42:42">
+      <c r="AP285" t="s">
         <v>677</v>
+      </c>
+    </row>
+    <row r="286" spans="42:42">
+      <c r="AP286" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="287" spans="42:42">
+      <c r="AP287" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="288" spans="42:42">
+      <c r="AP288" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="289" spans="42:42">
+      <c r="AP289" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="290" spans="42:42">
+      <c r="AP290" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="291" spans="42:42">
+      <c r="AP291" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="292" spans="42:42">
+      <c r="AP292" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="293" spans="42:42">
+      <c r="AP293" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="294" spans="42:42">
+      <c r="AP294" t="s">
+        <v>686</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000025/metadata_template_ERC000025.xlsx
+++ b/templates/ERC000025/metadata_template_ERC000025.xlsx
@@ -18,25 +18,25 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AP$1:$AP$294</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AQ$1:$AQ$294</definedName>
     <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="observedbioticrelationship">'cv_sample'!$G$1:$G$5</definedName>
-    <definedName name="oxygenationstatusofsample">'cv_sample'!$O$1:$O$2</definedName>
+    <definedName name="observedbioticrelationship">'cv_sample'!$H$1:$H$5</definedName>
+    <definedName name="oxygenationstatusofsample">'cv_sample'!$P$1:$P$2</definedName>
     <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
-    <definedName name="relationshiptooxygen">'cv_sample'!$I$1:$I$7</definedName>
-    <definedName name="sequencequalitycheck">'cv_sample'!$Y$1:$Y$3</definedName>
+    <definedName name="relationshiptooxygen">'cv_sample'!$J$1:$J$7</definedName>
+    <definedName name="sequencequalitycheck">'cv_sample'!$Z$1:$Z$3</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
-    <definedName name="trophiclevel">'cv_sample'!$F$1:$F$30</definedName>
+    <definedName name="trophiclevel">'cv_sample'!$G$1:$G$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="803">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="805">
   <si>
     <t>alias</t>
   </si>
@@ -852,6 +852,12 @@
   </si>
   <si>
     <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
+    <t>common_name</t>
+  </si>
+  <si>
+    <t>(Optional) Genbank common name of the organism.  examples: human, mouse.</t>
   </si>
   <si>
     <t>sample_description</t>
@@ -3968,13 +3974,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CU2"/>
+  <dimension ref="A1:CV2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:99">
+    <row r="1" spans="1:100">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3991,16 +3997,16 @@
         <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>304</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>313</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>324</v>
@@ -4018,7 +4024,7 @@
         <v>332</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>338</v>
@@ -4048,7 +4054,7 @@
         <v>354</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>361</v>
@@ -4099,7 +4105,7 @@
         <v>391</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>687</v>
+        <v>393</v>
       </c>
       <c r="AQ1" s="1" t="s">
         <v>689</v>
@@ -4272,8 +4278,11 @@
       <c r="CU1" s="1" t="s">
         <v>801</v>
       </c>
-    </row>
-    <row r="2" spans="1:99" ht="150" customHeight="1">
+      <c r="CV1" s="1" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="2" spans="1:100" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>266</v>
       </c>
@@ -4290,16 +4299,16 @@
         <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>305</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>314</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>325</v>
@@ -4317,7 +4326,7 @@
         <v>333</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>339</v>
@@ -4347,7 +4356,7 @@
         <v>355</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="Z2" s="2" t="s">
         <v>362</v>
@@ -4398,7 +4407,7 @@
         <v>392</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>688</v>
+        <v>394</v>
       </c>
       <c r="AQ2" s="2" t="s">
         <v>690</v>
@@ -4571,25 +4580,28 @@
       <c r="CU2" s="2" t="s">
         <v>802</v>
       </c>
+      <c r="CV2" s="2" t="s">
+        <v>804</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
       <formula1>trophiclevel</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
       <formula1>observedbioticrelationship</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J101">
       <formula1>relationshiptooxygen</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:P101">
       <formula1>oxygenationstatusofsample</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3:Y101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z3:Z101">
       <formula1>sequencequalitycheck</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AP3:AP101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ3:AQ101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
   </dataValidations>
@@ -4599,1618 +4611,1618 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="F1:AP294"/>
+  <dimension ref="G1:AQ294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="6:42">
-      <c r="F1" t="s">
-        <v>274</v>
-      </c>
+    <row r="1" spans="7:43">
       <c r="G1" t="s">
-        <v>306</v>
-      </c>
-      <c r="I1" t="s">
-        <v>315</v>
-      </c>
-      <c r="O1" t="s">
-        <v>334</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>356</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="2" spans="6:42">
-      <c r="F2" t="s">
-        <v>275</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="H1" t="s">
+        <v>308</v>
+      </c>
+      <c r="J1" t="s">
+        <v>317</v>
+      </c>
+      <c r="P1" t="s">
+        <v>336</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>358</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="2" spans="7:43">
       <c r="G2" t="s">
-        <v>307</v>
-      </c>
-      <c r="I2" t="s">
-        <v>316</v>
-      </c>
-      <c r="O2" t="s">
-        <v>335</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>357</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="3" spans="6:42">
-      <c r="F3" t="s">
-        <v>276</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="H2" t="s">
+        <v>309</v>
+      </c>
+      <c r="J2" t="s">
+        <v>318</v>
+      </c>
+      <c r="P2" t="s">
+        <v>337</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>359</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="3" spans="7:43">
       <c r="G3" t="s">
-        <v>308</v>
-      </c>
-      <c r="I3" t="s">
-        <v>317</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>358</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="4" spans="6:42">
-      <c r="F4" t="s">
-        <v>277</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="H3" t="s">
+        <v>310</v>
+      </c>
+      <c r="J3" t="s">
+        <v>319</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>360</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="4" spans="7:43">
       <c r="G4" t="s">
-        <v>309</v>
-      </c>
-      <c r="I4" t="s">
-        <v>318</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="5" spans="6:42">
-      <c r="F5" t="s">
-        <v>278</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="H4" t="s">
+        <v>311</v>
+      </c>
+      <c r="J4" t="s">
+        <v>320</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="5" spans="7:43">
       <c r="G5" t="s">
-        <v>310</v>
-      </c>
-      <c r="I5" t="s">
-        <v>319</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="6" spans="6:42">
-      <c r="F6" t="s">
-        <v>279</v>
-      </c>
-      <c r="I6" t="s">
-        <v>320</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="7" spans="6:42">
-      <c r="F7" t="s">
         <v>280</v>
       </c>
-      <c r="I7" t="s">
+      <c r="H5" t="s">
+        <v>312</v>
+      </c>
+      <c r="J5" t="s">
         <v>321</v>
       </c>
-      <c r="AP7" t="s">
+      <c r="AQ5" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="8" spans="6:42">
-      <c r="F8" t="s">
+    <row r="6" spans="7:43">
+      <c r="G6" t="s">
         <v>281</v>
       </c>
-      <c r="AP8" t="s">
+      <c r="J6" t="s">
+        <v>322</v>
+      </c>
+      <c r="AQ6" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="9" spans="6:42">
-      <c r="F9" t="s">
+    <row r="7" spans="7:43">
+      <c r="G7" t="s">
         <v>282</v>
       </c>
-      <c r="AP9" t="s">
+      <c r="J7" t="s">
+        <v>323</v>
+      </c>
+      <c r="AQ7" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="10" spans="6:42">
-      <c r="F10" t="s">
+    <row r="8" spans="7:43">
+      <c r="G8" t="s">
         <v>283</v>
       </c>
-      <c r="AP10" t="s">
+      <c r="AQ8" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="11" spans="6:42">
-      <c r="F11" t="s">
+    <row r="9" spans="7:43">
+      <c r="G9" t="s">
         <v>284</v>
       </c>
-      <c r="AP11" t="s">
+      <c r="AQ9" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="12" spans="6:42">
-      <c r="F12" t="s">
+    <row r="10" spans="7:43">
+      <c r="G10" t="s">
         <v>285</v>
       </c>
-      <c r="AP12" t="s">
+      <c r="AQ10" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="13" spans="6:42">
-      <c r="F13" t="s">
+    <row r="11" spans="7:43">
+      <c r="G11" t="s">
         <v>286</v>
       </c>
-      <c r="AP13" t="s">
+      <c r="AQ11" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="14" spans="6:42">
-      <c r="F14" t="s">
+    <row r="12" spans="7:43">
+      <c r="G12" t="s">
         <v>287</v>
       </c>
-      <c r="AP14" t="s">
+      <c r="AQ12" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="15" spans="6:42">
-      <c r="F15" t="s">
+    <row r="13" spans="7:43">
+      <c r="G13" t="s">
         <v>288</v>
       </c>
-      <c r="AP15" t="s">
+      <c r="AQ13" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="16" spans="6:42">
-      <c r="F16" t="s">
+    <row r="14" spans="7:43">
+      <c r="G14" t="s">
         <v>289</v>
       </c>
-      <c r="AP16" t="s">
+      <c r="AQ14" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="17" spans="6:42">
-      <c r="F17" t="s">
+    <row r="15" spans="7:43">
+      <c r="G15" t="s">
         <v>290</v>
       </c>
-      <c r="AP17" t="s">
+      <c r="AQ15" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="18" spans="6:42">
-      <c r="F18" t="s">
+    <row r="16" spans="7:43">
+      <c r="G16" t="s">
         <v>291</v>
       </c>
-      <c r="AP18" t="s">
+      <c r="AQ16" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="19" spans="6:42">
-      <c r="F19" t="s">
+    <row r="17" spans="7:43">
+      <c r="G17" t="s">
         <v>292</v>
       </c>
-      <c r="AP19" t="s">
+      <c r="AQ17" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="20" spans="6:42">
-      <c r="F20" t="s">
+    <row r="18" spans="7:43">
+      <c r="G18" t="s">
         <v>293</v>
       </c>
-      <c r="AP20" t="s">
+      <c r="AQ18" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="21" spans="6:42">
-      <c r="F21" t="s">
+    <row r="19" spans="7:43">
+      <c r="G19" t="s">
         <v>294</v>
       </c>
-      <c r="AP21" t="s">
+      <c r="AQ19" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="22" spans="6:42">
-      <c r="F22" t="s">
+    <row r="20" spans="7:43">
+      <c r="G20" t="s">
         <v>295</v>
       </c>
-      <c r="AP22" t="s">
+      <c r="AQ20" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="23" spans="6:42">
-      <c r="F23" t="s">
+    <row r="21" spans="7:43">
+      <c r="G21" t="s">
         <v>296</v>
       </c>
-      <c r="AP23" t="s">
+      <c r="AQ21" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="24" spans="6:42">
-      <c r="F24" t="s">
+    <row r="22" spans="7:43">
+      <c r="G22" t="s">
         <v>297</v>
       </c>
-      <c r="AP24" t="s">
+      <c r="AQ22" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="25" spans="6:42">
-      <c r="F25" t="s">
+    <row r="23" spans="7:43">
+      <c r="G23" t="s">
         <v>298</v>
       </c>
-      <c r="AP25" t="s">
+      <c r="AQ23" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="26" spans="6:42">
-      <c r="F26" t="s">
+    <row r="24" spans="7:43">
+      <c r="G24" t="s">
         <v>299</v>
       </c>
-      <c r="AP26" t="s">
+      <c r="AQ24" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="27" spans="6:42">
-      <c r="F27" t="s">
+    <row r="25" spans="7:43">
+      <c r="G25" t="s">
         <v>300</v>
       </c>
-      <c r="AP27" t="s">
+      <c r="AQ25" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="28" spans="6:42">
-      <c r="F28" t="s">
+    <row r="26" spans="7:43">
+      <c r="G26" t="s">
         <v>301</v>
       </c>
-      <c r="AP28" t="s">
+      <c r="AQ26" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="29" spans="6:42">
-      <c r="F29" t="s">
+    <row r="27" spans="7:43">
+      <c r="G27" t="s">
         <v>302</v>
       </c>
-      <c r="AP29" t="s">
+      <c r="AQ27" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="30" spans="6:42">
-      <c r="F30" t="s">
+    <row r="28" spans="7:43">
+      <c r="G28" t="s">
         <v>303</v>
       </c>
-      <c r="AP30" t="s">
+      <c r="AQ28" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="31" spans="6:42">
-      <c r="AP31" t="s">
+    <row r="29" spans="7:43">
+      <c r="G29" t="s">
+        <v>304</v>
+      </c>
+      <c r="AQ29" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="32" spans="6:42">
-      <c r="AP32" t="s">
+    <row r="30" spans="7:43">
+      <c r="G30" t="s">
+        <v>305</v>
+      </c>
+      <c r="AQ30" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="33" spans="42:42">
-      <c r="AP33" t="s">
+    <row r="31" spans="7:43">
+      <c r="AQ31" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="34" spans="42:42">
-      <c r="AP34" t="s">
+    <row r="32" spans="7:43">
+      <c r="AQ32" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="35" spans="42:42">
-      <c r="AP35" t="s">
+    <row r="33" spans="43:43">
+      <c r="AQ33" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="36" spans="42:42">
-      <c r="AP36" t="s">
+    <row r="34" spans="43:43">
+      <c r="AQ34" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="37" spans="42:42">
-      <c r="AP37" t="s">
+    <row r="35" spans="43:43">
+      <c r="AQ35" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="38" spans="42:42">
-      <c r="AP38" t="s">
+    <row r="36" spans="43:43">
+      <c r="AQ36" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="39" spans="42:42">
-      <c r="AP39" t="s">
+    <row r="37" spans="43:43">
+      <c r="AQ37" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="40" spans="42:42">
-      <c r="AP40" t="s">
+    <row r="38" spans="43:43">
+      <c r="AQ38" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="41" spans="42:42">
-      <c r="AP41" t="s">
+    <row r="39" spans="43:43">
+      <c r="AQ39" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="42" spans="42:42">
-      <c r="AP42" t="s">
+    <row r="40" spans="43:43">
+      <c r="AQ40" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="43" spans="42:42">
-      <c r="AP43" t="s">
+    <row r="41" spans="43:43">
+      <c r="AQ41" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="44" spans="42:42">
-      <c r="AP44" t="s">
+    <row r="42" spans="43:43">
+      <c r="AQ42" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="45" spans="42:42">
-      <c r="AP45" t="s">
+    <row r="43" spans="43:43">
+      <c r="AQ43" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="46" spans="42:42">
-      <c r="AP46" t="s">
+    <row r="44" spans="43:43">
+      <c r="AQ44" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="47" spans="42:42">
-      <c r="AP47" t="s">
+    <row r="45" spans="43:43">
+      <c r="AQ45" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="48" spans="42:42">
-      <c r="AP48" t="s">
+    <row r="46" spans="43:43">
+      <c r="AQ46" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="49" spans="42:42">
-      <c r="AP49" t="s">
+    <row r="47" spans="43:43">
+      <c r="AQ47" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="50" spans="42:42">
-      <c r="AP50" t="s">
+    <row r="48" spans="43:43">
+      <c r="AQ48" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="51" spans="42:42">
-      <c r="AP51" t="s">
+    <row r="49" spans="43:43">
+      <c r="AQ49" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="52" spans="42:42">
-      <c r="AP52" t="s">
+    <row r="50" spans="43:43">
+      <c r="AQ50" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="53" spans="42:42">
-      <c r="AP53" t="s">
+    <row r="51" spans="43:43">
+      <c r="AQ51" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="54" spans="42:42">
-      <c r="AP54" t="s">
+    <row r="52" spans="43:43">
+      <c r="AQ52" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="55" spans="42:42">
-      <c r="AP55" t="s">
+    <row r="53" spans="43:43">
+      <c r="AQ53" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="56" spans="42:42">
-      <c r="AP56" t="s">
+    <row r="54" spans="43:43">
+      <c r="AQ54" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="57" spans="42:42">
-      <c r="AP57" t="s">
+    <row r="55" spans="43:43">
+      <c r="AQ55" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="58" spans="42:42">
-      <c r="AP58" t="s">
+    <row r="56" spans="43:43">
+      <c r="AQ56" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="59" spans="42:42">
-      <c r="AP59" t="s">
+    <row r="57" spans="43:43">
+      <c r="AQ57" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="60" spans="42:42">
-      <c r="AP60" t="s">
+    <row r="58" spans="43:43">
+      <c r="AQ58" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="61" spans="42:42">
-      <c r="AP61" t="s">
+    <row r="59" spans="43:43">
+      <c r="AQ59" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="62" spans="42:42">
-      <c r="AP62" t="s">
+    <row r="60" spans="43:43">
+      <c r="AQ60" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="63" spans="42:42">
-      <c r="AP63" t="s">
+    <row r="61" spans="43:43">
+      <c r="AQ61" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="64" spans="42:42">
-      <c r="AP64" t="s">
+    <row r="62" spans="43:43">
+      <c r="AQ62" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="65" spans="42:42">
-      <c r="AP65" t="s">
+    <row r="63" spans="43:43">
+      <c r="AQ63" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="66" spans="42:42">
-      <c r="AP66" t="s">
+    <row r="64" spans="43:43">
+      <c r="AQ64" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="67" spans="42:42">
-      <c r="AP67" t="s">
+    <row r="65" spans="43:43">
+      <c r="AQ65" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="68" spans="42:42">
-      <c r="AP68" t="s">
+    <row r="66" spans="43:43">
+      <c r="AQ66" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="69" spans="42:42">
-      <c r="AP69" t="s">
+    <row r="67" spans="43:43">
+      <c r="AQ67" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="70" spans="42:42">
-      <c r="AP70" t="s">
+    <row r="68" spans="43:43">
+      <c r="AQ68" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="71" spans="42:42">
-      <c r="AP71" t="s">
+    <row r="69" spans="43:43">
+      <c r="AQ69" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="72" spans="42:42">
-      <c r="AP72" t="s">
+    <row r="70" spans="43:43">
+      <c r="AQ70" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="73" spans="42:42">
-      <c r="AP73" t="s">
+    <row r="71" spans="43:43">
+      <c r="AQ71" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="74" spans="42:42">
-      <c r="AP74" t="s">
+    <row r="72" spans="43:43">
+      <c r="AQ72" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="75" spans="42:42">
-      <c r="AP75" t="s">
+    <row r="73" spans="43:43">
+      <c r="AQ73" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="76" spans="42:42">
-      <c r="AP76" t="s">
+    <row r="74" spans="43:43">
+      <c r="AQ74" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="77" spans="42:42">
-      <c r="AP77" t="s">
+    <row r="75" spans="43:43">
+      <c r="AQ75" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="78" spans="42:42">
-      <c r="AP78" t="s">
+    <row r="76" spans="43:43">
+      <c r="AQ76" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="79" spans="42:42">
-      <c r="AP79" t="s">
+    <row r="77" spans="43:43">
+      <c r="AQ77" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="80" spans="42:42">
-      <c r="AP80" t="s">
+    <row r="78" spans="43:43">
+      <c r="AQ78" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="81" spans="42:42">
-      <c r="AP81" t="s">
+    <row r="79" spans="43:43">
+      <c r="AQ79" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="82" spans="42:42">
-      <c r="AP82" t="s">
+    <row r="80" spans="43:43">
+      <c r="AQ80" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="83" spans="42:42">
-      <c r="AP83" t="s">
+    <row r="81" spans="43:43">
+      <c r="AQ81" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="84" spans="42:42">
-      <c r="AP84" t="s">
+    <row r="82" spans="43:43">
+      <c r="AQ82" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="85" spans="42:42">
-      <c r="AP85" t="s">
+    <row r="83" spans="43:43">
+      <c r="AQ83" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="86" spans="42:42">
-      <c r="AP86" t="s">
+    <row r="84" spans="43:43">
+      <c r="AQ84" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="87" spans="42:42">
-      <c r="AP87" t="s">
+    <row r="85" spans="43:43">
+      <c r="AQ85" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="88" spans="42:42">
-      <c r="AP88" t="s">
+    <row r="86" spans="43:43">
+      <c r="AQ86" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="89" spans="42:42">
-      <c r="AP89" t="s">
+    <row r="87" spans="43:43">
+      <c r="AQ87" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="90" spans="42:42">
-      <c r="AP90" t="s">
+    <row r="88" spans="43:43">
+      <c r="AQ88" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="91" spans="42:42">
-      <c r="AP91" t="s">
+    <row r="89" spans="43:43">
+      <c r="AQ89" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="92" spans="42:42">
-      <c r="AP92" t="s">
+    <row r="90" spans="43:43">
+      <c r="AQ90" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="93" spans="42:42">
-      <c r="AP93" t="s">
+    <row r="91" spans="43:43">
+      <c r="AQ91" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="94" spans="42:42">
-      <c r="AP94" t="s">
+    <row r="92" spans="43:43">
+      <c r="AQ92" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="95" spans="42:42">
-      <c r="AP95" t="s">
+    <row r="93" spans="43:43">
+      <c r="AQ93" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="96" spans="42:42">
-      <c r="AP96" t="s">
+    <row r="94" spans="43:43">
+      <c r="AQ94" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="97" spans="42:42">
-      <c r="AP97" t="s">
+    <row r="95" spans="43:43">
+      <c r="AQ95" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="98" spans="42:42">
-      <c r="AP98" t="s">
+    <row r="96" spans="43:43">
+      <c r="AQ96" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="99" spans="42:42">
-      <c r="AP99" t="s">
+    <row r="97" spans="43:43">
+      <c r="AQ97" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="100" spans="42:42">
-      <c r="AP100" t="s">
+    <row r="98" spans="43:43">
+      <c r="AQ98" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="101" spans="42:42">
-      <c r="AP101" t="s">
+    <row r="99" spans="43:43">
+      <c r="AQ99" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="102" spans="42:42">
-      <c r="AP102" t="s">
+    <row r="100" spans="43:43">
+      <c r="AQ100" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="103" spans="42:42">
-      <c r="AP103" t="s">
+    <row r="101" spans="43:43">
+      <c r="AQ101" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="104" spans="42:42">
-      <c r="AP104" t="s">
+    <row r="102" spans="43:43">
+      <c r="AQ102" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="105" spans="42:42">
-      <c r="AP105" t="s">
+    <row r="103" spans="43:43">
+      <c r="AQ103" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="106" spans="42:42">
-      <c r="AP106" t="s">
+    <row r="104" spans="43:43">
+      <c r="AQ104" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="107" spans="42:42">
-      <c r="AP107" t="s">
+    <row r="105" spans="43:43">
+      <c r="AQ105" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="108" spans="42:42">
-      <c r="AP108" t="s">
+    <row r="106" spans="43:43">
+      <c r="AQ106" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="109" spans="42:42">
-      <c r="AP109" t="s">
+    <row r="107" spans="43:43">
+      <c r="AQ107" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="110" spans="42:42">
-      <c r="AP110" t="s">
+    <row r="108" spans="43:43">
+      <c r="AQ108" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="111" spans="42:42">
-      <c r="AP111" t="s">
+    <row r="109" spans="43:43">
+      <c r="AQ109" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="112" spans="42:42">
-      <c r="AP112" t="s">
+    <row r="110" spans="43:43">
+      <c r="AQ110" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="113" spans="42:42">
-      <c r="AP113" t="s">
+    <row r="111" spans="43:43">
+      <c r="AQ111" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="114" spans="42:42">
-      <c r="AP114" t="s">
+    <row r="112" spans="43:43">
+      <c r="AQ112" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="115" spans="42:42">
-      <c r="AP115" t="s">
+    <row r="113" spans="43:43">
+      <c r="AQ113" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="116" spans="42:42">
-      <c r="AP116" t="s">
+    <row r="114" spans="43:43">
+      <c r="AQ114" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="117" spans="42:42">
-      <c r="AP117" t="s">
+    <row r="115" spans="43:43">
+      <c r="AQ115" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="118" spans="42:42">
-      <c r="AP118" t="s">
+    <row r="116" spans="43:43">
+      <c r="AQ116" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="119" spans="42:42">
-      <c r="AP119" t="s">
+    <row r="117" spans="43:43">
+      <c r="AQ117" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="120" spans="42:42">
-      <c r="AP120" t="s">
+    <row r="118" spans="43:43">
+      <c r="AQ118" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="121" spans="42:42">
-      <c r="AP121" t="s">
+    <row r="119" spans="43:43">
+      <c r="AQ119" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="122" spans="42:42">
-      <c r="AP122" t="s">
+    <row r="120" spans="43:43">
+      <c r="AQ120" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="123" spans="42:42">
-      <c r="AP123" t="s">
+    <row r="121" spans="43:43">
+      <c r="AQ121" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="124" spans="42:42">
-      <c r="AP124" t="s">
+    <row r="122" spans="43:43">
+      <c r="AQ122" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="125" spans="42:42">
-      <c r="AP125" t="s">
+    <row r="123" spans="43:43">
+      <c r="AQ123" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="126" spans="42:42">
-      <c r="AP126" t="s">
+    <row r="124" spans="43:43">
+      <c r="AQ124" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="127" spans="42:42">
-      <c r="AP127" t="s">
+    <row r="125" spans="43:43">
+      <c r="AQ125" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="128" spans="42:42">
-      <c r="AP128" t="s">
+    <row r="126" spans="43:43">
+      <c r="AQ126" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="129" spans="42:42">
-      <c r="AP129" t="s">
+    <row r="127" spans="43:43">
+      <c r="AQ127" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="130" spans="42:42">
-      <c r="AP130" t="s">
+    <row r="128" spans="43:43">
+      <c r="AQ128" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="131" spans="42:42">
-      <c r="AP131" t="s">
+    <row r="129" spans="43:43">
+      <c r="AQ129" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="132" spans="42:42">
-      <c r="AP132" t="s">
+    <row r="130" spans="43:43">
+      <c r="AQ130" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="133" spans="42:42">
-      <c r="AP133" t="s">
+    <row r="131" spans="43:43">
+      <c r="AQ131" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="134" spans="42:42">
-      <c r="AP134" t="s">
+    <row r="132" spans="43:43">
+      <c r="AQ132" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="135" spans="42:42">
-      <c r="AP135" t="s">
+    <row r="133" spans="43:43">
+      <c r="AQ133" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="136" spans="42:42">
-      <c r="AP136" t="s">
+    <row r="134" spans="43:43">
+      <c r="AQ134" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="137" spans="42:42">
-      <c r="AP137" t="s">
+    <row r="135" spans="43:43">
+      <c r="AQ135" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="138" spans="42:42">
-      <c r="AP138" t="s">
+    <row r="136" spans="43:43">
+      <c r="AQ136" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="139" spans="42:42">
-      <c r="AP139" t="s">
+    <row r="137" spans="43:43">
+      <c r="AQ137" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="140" spans="42:42">
-      <c r="AP140" t="s">
+    <row r="138" spans="43:43">
+      <c r="AQ138" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="141" spans="42:42">
-      <c r="AP141" t="s">
+    <row r="139" spans="43:43">
+      <c r="AQ139" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="142" spans="42:42">
-      <c r="AP142" t="s">
+    <row r="140" spans="43:43">
+      <c r="AQ140" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="143" spans="42:42">
-      <c r="AP143" t="s">
+    <row r="141" spans="43:43">
+      <c r="AQ141" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="144" spans="42:42">
-      <c r="AP144" t="s">
+    <row r="142" spans="43:43">
+      <c r="AQ142" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="145" spans="42:42">
-      <c r="AP145" t="s">
+    <row r="143" spans="43:43">
+      <c r="AQ143" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="146" spans="42:42">
-      <c r="AP146" t="s">
+    <row r="144" spans="43:43">
+      <c r="AQ144" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="147" spans="42:42">
-      <c r="AP147" t="s">
+    <row r="145" spans="43:43">
+      <c r="AQ145" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="148" spans="42:42">
-      <c r="AP148" t="s">
+    <row r="146" spans="43:43">
+      <c r="AQ146" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="149" spans="42:42">
-      <c r="AP149" t="s">
+    <row r="147" spans="43:43">
+      <c r="AQ147" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="150" spans="42:42">
-      <c r="AP150" t="s">
+    <row r="148" spans="43:43">
+      <c r="AQ148" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="151" spans="42:42">
-      <c r="AP151" t="s">
+    <row r="149" spans="43:43">
+      <c r="AQ149" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="152" spans="42:42">
-      <c r="AP152" t="s">
+    <row r="150" spans="43:43">
+      <c r="AQ150" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="153" spans="42:42">
-      <c r="AP153" t="s">
+    <row r="151" spans="43:43">
+      <c r="AQ151" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="154" spans="42:42">
-      <c r="AP154" t="s">
+    <row r="152" spans="43:43">
+      <c r="AQ152" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="155" spans="42:42">
-      <c r="AP155" t="s">
+    <row r="153" spans="43:43">
+      <c r="AQ153" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="156" spans="42:42">
-      <c r="AP156" t="s">
+    <row r="154" spans="43:43">
+      <c r="AQ154" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="157" spans="42:42">
-      <c r="AP157" t="s">
+    <row r="155" spans="43:43">
+      <c r="AQ155" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="158" spans="42:42">
-      <c r="AP158" t="s">
+    <row r="156" spans="43:43">
+      <c r="AQ156" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="159" spans="42:42">
-      <c r="AP159" t="s">
+    <row r="157" spans="43:43">
+      <c r="AQ157" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="160" spans="42:42">
-      <c r="AP160" t="s">
+    <row r="158" spans="43:43">
+      <c r="AQ158" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="161" spans="42:42">
-      <c r="AP161" t="s">
+    <row r="159" spans="43:43">
+      <c r="AQ159" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="162" spans="42:42">
-      <c r="AP162" t="s">
+    <row r="160" spans="43:43">
+      <c r="AQ160" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="163" spans="42:42">
-      <c r="AP163" t="s">
+    <row r="161" spans="43:43">
+      <c r="AQ161" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="164" spans="42:42">
-      <c r="AP164" t="s">
+    <row r="162" spans="43:43">
+      <c r="AQ162" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="165" spans="42:42">
-      <c r="AP165" t="s">
+    <row r="163" spans="43:43">
+      <c r="AQ163" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="166" spans="42:42">
-      <c r="AP166" t="s">
+    <row r="164" spans="43:43">
+      <c r="AQ164" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="167" spans="42:42">
-      <c r="AP167" t="s">
+    <row r="165" spans="43:43">
+      <c r="AQ165" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="168" spans="42:42">
-      <c r="AP168" t="s">
+    <row r="166" spans="43:43">
+      <c r="AQ166" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="169" spans="42:42">
-      <c r="AP169" t="s">
+    <row r="167" spans="43:43">
+      <c r="AQ167" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="170" spans="42:42">
-      <c r="AP170" t="s">
+    <row r="168" spans="43:43">
+      <c r="AQ168" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="171" spans="42:42">
-      <c r="AP171" t="s">
+    <row r="169" spans="43:43">
+      <c r="AQ169" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="172" spans="42:42">
-      <c r="AP172" t="s">
+    <row r="170" spans="43:43">
+      <c r="AQ170" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="173" spans="42:42">
-      <c r="AP173" t="s">
+    <row r="171" spans="43:43">
+      <c r="AQ171" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="174" spans="42:42">
-      <c r="AP174" t="s">
+    <row r="172" spans="43:43">
+      <c r="AQ172" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="175" spans="42:42">
-      <c r="AP175" t="s">
+    <row r="173" spans="43:43">
+      <c r="AQ173" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="176" spans="42:42">
-      <c r="AP176" t="s">
+    <row r="174" spans="43:43">
+      <c r="AQ174" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="177" spans="42:42">
-      <c r="AP177" t="s">
+    <row r="175" spans="43:43">
+      <c r="AQ175" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="178" spans="42:42">
-      <c r="AP178" t="s">
+    <row r="176" spans="43:43">
+      <c r="AQ176" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="179" spans="42:42">
-      <c r="AP179" t="s">
+    <row r="177" spans="43:43">
+      <c r="AQ177" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="180" spans="42:42">
-      <c r="AP180" t="s">
+    <row r="178" spans="43:43">
+      <c r="AQ178" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="181" spans="42:42">
-      <c r="AP181" t="s">
+    <row r="179" spans="43:43">
+      <c r="AQ179" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="182" spans="42:42">
-      <c r="AP182" t="s">
+    <row r="180" spans="43:43">
+      <c r="AQ180" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="183" spans="42:42">
-      <c r="AP183" t="s">
+    <row r="181" spans="43:43">
+      <c r="AQ181" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="184" spans="42:42">
-      <c r="AP184" t="s">
+    <row r="182" spans="43:43">
+      <c r="AQ182" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="185" spans="42:42">
-      <c r="AP185" t="s">
+    <row r="183" spans="43:43">
+      <c r="AQ183" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="186" spans="42:42">
-      <c r="AP186" t="s">
+    <row r="184" spans="43:43">
+      <c r="AQ184" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="187" spans="42:42">
-      <c r="AP187" t="s">
+    <row r="185" spans="43:43">
+      <c r="AQ185" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="188" spans="42:42">
-      <c r="AP188" t="s">
+    <row r="186" spans="43:43">
+      <c r="AQ186" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="189" spans="42:42">
-      <c r="AP189" t="s">
+    <row r="187" spans="43:43">
+      <c r="AQ187" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="190" spans="42:42">
-      <c r="AP190" t="s">
+    <row r="188" spans="43:43">
+      <c r="AQ188" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="191" spans="42:42">
-      <c r="AP191" t="s">
+    <row r="189" spans="43:43">
+      <c r="AQ189" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="192" spans="42:42">
-      <c r="AP192" t="s">
+    <row r="190" spans="43:43">
+      <c r="AQ190" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="193" spans="42:42">
-      <c r="AP193" t="s">
+    <row r="191" spans="43:43">
+      <c r="AQ191" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="194" spans="42:42">
-      <c r="AP194" t="s">
+    <row r="192" spans="43:43">
+      <c r="AQ192" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="195" spans="42:42">
-      <c r="AP195" t="s">
+    <row r="193" spans="43:43">
+      <c r="AQ193" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="196" spans="42:42">
-      <c r="AP196" t="s">
+    <row r="194" spans="43:43">
+      <c r="AQ194" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="197" spans="42:42">
-      <c r="AP197" t="s">
+    <row r="195" spans="43:43">
+      <c r="AQ195" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="198" spans="42:42">
-      <c r="AP198" t="s">
+    <row r="196" spans="43:43">
+      <c r="AQ196" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="199" spans="42:42">
-      <c r="AP199" t="s">
+    <row r="197" spans="43:43">
+      <c r="AQ197" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="200" spans="42:42">
-      <c r="AP200" t="s">
+    <row r="198" spans="43:43">
+      <c r="AQ198" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="201" spans="42:42">
-      <c r="AP201" t="s">
+    <row r="199" spans="43:43">
+      <c r="AQ199" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="202" spans="42:42">
-      <c r="AP202" t="s">
+    <row r="200" spans="43:43">
+      <c r="AQ200" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="203" spans="42:42">
-      <c r="AP203" t="s">
+    <row r="201" spans="43:43">
+      <c r="AQ201" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="204" spans="42:42">
-      <c r="AP204" t="s">
+    <row r="202" spans="43:43">
+      <c r="AQ202" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="205" spans="42:42">
-      <c r="AP205" t="s">
+    <row r="203" spans="43:43">
+      <c r="AQ203" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="206" spans="42:42">
-      <c r="AP206" t="s">
+    <row r="204" spans="43:43">
+      <c r="AQ204" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="207" spans="42:42">
-      <c r="AP207" t="s">
+    <row r="205" spans="43:43">
+      <c r="AQ205" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="208" spans="42:42">
-      <c r="AP208" t="s">
+    <row r="206" spans="43:43">
+      <c r="AQ206" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="209" spans="42:42">
-      <c r="AP209" t="s">
+    <row r="207" spans="43:43">
+      <c r="AQ207" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="210" spans="42:42">
-      <c r="AP210" t="s">
+    <row r="208" spans="43:43">
+      <c r="AQ208" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="211" spans="42:42">
-      <c r="AP211" t="s">
+    <row r="209" spans="43:43">
+      <c r="AQ209" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="212" spans="42:42">
-      <c r="AP212" t="s">
+    <row r="210" spans="43:43">
+      <c r="AQ210" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="213" spans="42:42">
-      <c r="AP213" t="s">
+    <row r="211" spans="43:43">
+      <c r="AQ211" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="214" spans="42:42">
-      <c r="AP214" t="s">
+    <row r="212" spans="43:43">
+      <c r="AQ212" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="215" spans="42:42">
-      <c r="AP215" t="s">
+    <row r="213" spans="43:43">
+      <c r="AQ213" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="216" spans="42:42">
-      <c r="AP216" t="s">
+    <row r="214" spans="43:43">
+      <c r="AQ214" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="217" spans="42:42">
-      <c r="AP217" t="s">
+    <row r="215" spans="43:43">
+      <c r="AQ215" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="218" spans="42:42">
-      <c r="AP218" t="s">
+    <row r="216" spans="43:43">
+      <c r="AQ216" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="219" spans="42:42">
-      <c r="AP219" t="s">
+    <row r="217" spans="43:43">
+      <c r="AQ217" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="220" spans="42:42">
-      <c r="AP220" t="s">
+    <row r="218" spans="43:43">
+      <c r="AQ218" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="221" spans="42:42">
-      <c r="AP221" t="s">
+    <row r="219" spans="43:43">
+      <c r="AQ219" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="222" spans="42:42">
-      <c r="AP222" t="s">
+    <row r="220" spans="43:43">
+      <c r="AQ220" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="223" spans="42:42">
-      <c r="AP223" t="s">
+    <row r="221" spans="43:43">
+      <c r="AQ221" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="224" spans="42:42">
-      <c r="AP224" t="s">
+    <row r="222" spans="43:43">
+      <c r="AQ222" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="225" spans="42:42">
-      <c r="AP225" t="s">
+    <row r="223" spans="43:43">
+      <c r="AQ223" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="226" spans="42:42">
-      <c r="AP226" t="s">
+    <row r="224" spans="43:43">
+      <c r="AQ224" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="227" spans="42:42">
-      <c r="AP227" t="s">
+    <row r="225" spans="43:43">
+      <c r="AQ225" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="228" spans="42:42">
-      <c r="AP228" t="s">
+    <row r="226" spans="43:43">
+      <c r="AQ226" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="229" spans="42:42">
-      <c r="AP229" t="s">
+    <row r="227" spans="43:43">
+      <c r="AQ227" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="230" spans="42:42">
-      <c r="AP230" t="s">
+    <row r="228" spans="43:43">
+      <c r="AQ228" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="231" spans="42:42">
-      <c r="AP231" t="s">
+    <row r="229" spans="43:43">
+      <c r="AQ229" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="232" spans="42:42">
-      <c r="AP232" t="s">
+    <row r="230" spans="43:43">
+      <c r="AQ230" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="233" spans="42:42">
-      <c r="AP233" t="s">
+    <row r="231" spans="43:43">
+      <c r="AQ231" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="234" spans="42:42">
-      <c r="AP234" t="s">
+    <row r="232" spans="43:43">
+      <c r="AQ232" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="235" spans="42:42">
-      <c r="AP235" t="s">
+    <row r="233" spans="43:43">
+      <c r="AQ233" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="236" spans="42:42">
-      <c r="AP236" t="s">
+    <row r="234" spans="43:43">
+      <c r="AQ234" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="237" spans="42:42">
-      <c r="AP237" t="s">
+    <row r="235" spans="43:43">
+      <c r="AQ235" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="238" spans="42:42">
-      <c r="AP238" t="s">
+    <row r="236" spans="43:43">
+      <c r="AQ236" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="239" spans="42:42">
-      <c r="AP239" t="s">
+    <row r="237" spans="43:43">
+      <c r="AQ237" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="240" spans="42:42">
-      <c r="AP240" t="s">
+    <row r="238" spans="43:43">
+      <c r="AQ238" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="241" spans="42:42">
-      <c r="AP241" t="s">
+    <row r="239" spans="43:43">
+      <c r="AQ239" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="242" spans="42:42">
-      <c r="AP242" t="s">
+    <row r="240" spans="43:43">
+      <c r="AQ240" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="243" spans="42:42">
-      <c r="AP243" t="s">
+    <row r="241" spans="43:43">
+      <c r="AQ241" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="244" spans="42:42">
-      <c r="AP244" t="s">
+    <row r="242" spans="43:43">
+      <c r="AQ242" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="245" spans="42:42">
-      <c r="AP245" t="s">
+    <row r="243" spans="43:43">
+      <c r="AQ243" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="246" spans="42:42">
-      <c r="AP246" t="s">
+    <row r="244" spans="43:43">
+      <c r="AQ244" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="247" spans="42:42">
-      <c r="AP247" t="s">
+    <row r="245" spans="43:43">
+      <c r="AQ245" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="248" spans="42:42">
-      <c r="AP248" t="s">
+    <row r="246" spans="43:43">
+      <c r="AQ246" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="249" spans="42:42">
-      <c r="AP249" t="s">
+    <row r="247" spans="43:43">
+      <c r="AQ247" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="250" spans="42:42">
-      <c r="AP250" t="s">
+    <row r="248" spans="43:43">
+      <c r="AQ248" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="251" spans="42:42">
-      <c r="AP251" t="s">
+    <row r="249" spans="43:43">
+      <c r="AQ249" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="252" spans="42:42">
-      <c r="AP252" t="s">
+    <row r="250" spans="43:43">
+      <c r="AQ250" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="253" spans="42:42">
-      <c r="AP253" t="s">
+    <row r="251" spans="43:43">
+      <c r="AQ251" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="254" spans="42:42">
-      <c r="AP254" t="s">
+    <row r="252" spans="43:43">
+      <c r="AQ252" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="255" spans="42:42">
-      <c r="AP255" t="s">
+    <row r="253" spans="43:43">
+      <c r="AQ253" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="256" spans="42:42">
-      <c r="AP256" t="s">
+    <row r="254" spans="43:43">
+      <c r="AQ254" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="257" spans="42:42">
-      <c r="AP257" t="s">
+    <row r="255" spans="43:43">
+      <c r="AQ255" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="258" spans="42:42">
-      <c r="AP258" t="s">
+    <row r="256" spans="43:43">
+      <c r="AQ256" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="259" spans="42:42">
-      <c r="AP259" t="s">
+    <row r="257" spans="43:43">
+      <c r="AQ257" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="260" spans="42:42">
-      <c r="AP260" t="s">
+    <row r="258" spans="43:43">
+      <c r="AQ258" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="261" spans="42:42">
-      <c r="AP261" t="s">
+    <row r="259" spans="43:43">
+      <c r="AQ259" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="262" spans="42:42">
-      <c r="AP262" t="s">
+    <row r="260" spans="43:43">
+      <c r="AQ260" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="263" spans="42:42">
-      <c r="AP263" t="s">
+    <row r="261" spans="43:43">
+      <c r="AQ261" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="264" spans="42:42">
-      <c r="AP264" t="s">
+    <row r="262" spans="43:43">
+      <c r="AQ262" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="265" spans="42:42">
-      <c r="AP265" t="s">
+    <row r="263" spans="43:43">
+      <c r="AQ263" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="266" spans="42:42">
-      <c r="AP266" t="s">
+    <row r="264" spans="43:43">
+      <c r="AQ264" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="267" spans="42:42">
-      <c r="AP267" t="s">
+    <row r="265" spans="43:43">
+      <c r="AQ265" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="268" spans="42:42">
-      <c r="AP268" t="s">
+    <row r="266" spans="43:43">
+      <c r="AQ266" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="269" spans="42:42">
-      <c r="AP269" t="s">
+    <row r="267" spans="43:43">
+      <c r="AQ267" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="270" spans="42:42">
-      <c r="AP270" t="s">
+    <row r="268" spans="43:43">
+      <c r="AQ268" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="271" spans="42:42">
-      <c r="AP271" t="s">
+    <row r="269" spans="43:43">
+      <c r="AQ269" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="272" spans="42:42">
-      <c r="AP272" t="s">
+    <row r="270" spans="43:43">
+      <c r="AQ270" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="273" spans="42:42">
-      <c r="AP273" t="s">
+    <row r="271" spans="43:43">
+      <c r="AQ271" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="274" spans="42:42">
-      <c r="AP274" t="s">
+    <row r="272" spans="43:43">
+      <c r="AQ272" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="275" spans="42:42">
-      <c r="AP275" t="s">
+    <row r="273" spans="43:43">
+      <c r="AQ273" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="276" spans="42:42">
-      <c r="AP276" t="s">
+    <row r="274" spans="43:43">
+      <c r="AQ274" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="277" spans="42:42">
-      <c r="AP277" t="s">
+    <row r="275" spans="43:43">
+      <c r="AQ275" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="278" spans="42:42">
-      <c r="AP278" t="s">
+    <row r="276" spans="43:43">
+      <c r="AQ276" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="279" spans="42:42">
-      <c r="AP279" t="s">
+    <row r="277" spans="43:43">
+      <c r="AQ277" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="280" spans="42:42">
-      <c r="AP280" t="s">
+    <row r="278" spans="43:43">
+      <c r="AQ278" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="281" spans="42:42">
-      <c r="AP281" t="s">
+    <row r="279" spans="43:43">
+      <c r="AQ279" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="282" spans="42:42">
-      <c r="AP282" t="s">
+    <row r="280" spans="43:43">
+      <c r="AQ280" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="283" spans="42:42">
-      <c r="AP283" t="s">
+    <row r="281" spans="43:43">
+      <c r="AQ281" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="284" spans="42:42">
-      <c r="AP284" t="s">
+    <row r="282" spans="43:43">
+      <c r="AQ282" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="285" spans="42:42">
-      <c r="AP285" t="s">
+    <row r="283" spans="43:43">
+      <c r="AQ283" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="286" spans="42:42">
-      <c r="AP286" t="s">
+    <row r="284" spans="43:43">
+      <c r="AQ284" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="287" spans="42:42">
-      <c r="AP287" t="s">
+    <row r="285" spans="43:43">
+      <c r="AQ285" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="288" spans="42:42">
-      <c r="AP288" t="s">
+    <row r="286" spans="43:43">
+      <c r="AQ286" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="289" spans="42:42">
-      <c r="AP289" t="s">
+    <row r="287" spans="43:43">
+      <c r="AQ287" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="290" spans="42:42">
-      <c r="AP290" t="s">
+    <row r="288" spans="43:43">
+      <c r="AQ288" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="291" spans="42:42">
-      <c r="AP291" t="s">
+    <row r="289" spans="43:43">
+      <c r="AQ289" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="292" spans="42:42">
-      <c r="AP292" t="s">
+    <row r="290" spans="43:43">
+      <c r="AQ290" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="293" spans="42:42">
-      <c r="AP293" t="s">
+    <row r="291" spans="43:43">
+      <c r="AQ291" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="294" spans="42:42">
-      <c r="AP294" t="s">
+    <row r="292" spans="43:43">
+      <c r="AQ292" t="s">
         <v>686</v>
+      </c>
+    </row>
+    <row r="293" spans="43:43">
+      <c r="AQ293" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="294" spans="43:43">
+      <c r="AQ294" t="s">
+        <v>688</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000025/metadata_template_ERC000025.xlsx
+++ b/templates/ERC000025/metadata_template_ERC000025.xlsx
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AQ$1:$AQ$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AQ$1:$AQ$294</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
     <definedName name="observedbioticrelationship">'cv_sample'!$H$1:$H$5</definedName>
     <definedName name="oxygenationstatusofsample">'cv_sample'!$P$1:$P$2</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="relationshiptooxygen">'cv_sample'!$J$1:$J$7</definedName>
     <definedName name="sequencequalitycheck">'cv_sample'!$Z$1:$Z$3</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="805">
   <si>
     <t>alias</t>
   </si>
@@ -452,6 +452,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -542,6 +545,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1430,9 +1436,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1451,6 +1454,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1652,6 +1658,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1661,9 +1670,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1703,7 +1709,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1772,6 +1778,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1847,6 +1856,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1868,6 +1880,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1913,6 +1928,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1925,6 +1943,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1934,9 +1955,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1961,6 +1979,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2021,10 +2042,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -2956,10 +2977,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3000,10 +3021,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -3030,7 +3051,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3047,7 +3068,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -3064,7 +3085,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -3081,7 +3102,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -3098,7 +3119,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -3115,7 +3136,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -3132,7 +3153,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -3149,7 +3170,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -3166,7 +3187,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -3183,7 +3204,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -3197,7 +3218,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -3211,7 +3232,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -3225,7 +3246,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -3239,7 +3260,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -3253,7 +3274,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -3267,7 +3288,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -3281,7 +3302,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -3295,7 +3316,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -3305,8 +3326,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -3317,7 +3341,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -3328,7 +3352,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -3339,7 +3363,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3350,7 +3374,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3361,7 +3385,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3372,7 +3396,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3383,7 +3407,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3394,7 +3418,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3405,7 +3429,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3416,7 +3440,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3427,7 +3451,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3438,7 +3462,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3449,7 +3473,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3457,7 +3481,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3465,7 +3489,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3473,7 +3497,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3481,7 +3505,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3489,7 +3513,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3497,7 +3521,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3505,7 +3529,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3513,7 +3537,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3521,7 +3545,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3529,236 +3553,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3780,27 +3809,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3820,122 +3849,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3959,600 +3988,600 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
     </row>
     <row r="2" spans="1:100" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -4582,1593 +4611,1618 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:AQ289"/>
+  <dimension ref="G1:AQ294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:43">
       <c r="G1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="P1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Z1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AQ1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2" spans="7:43">
       <c r="G2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="P2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Z2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AQ2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="3" spans="7:43">
       <c r="G3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Z3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AQ3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4" spans="7:43">
       <c r="G4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AQ4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="5" spans="7:43">
       <c r="G5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AQ5" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="6" spans="7:43">
       <c r="G6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AQ6" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" spans="7:43">
       <c r="G7" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AQ7" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="8" spans="7:43">
       <c r="G8" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AQ8" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="7:43">
       <c r="G9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AQ9" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="10" spans="7:43">
       <c r="G10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AQ10" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="11" spans="7:43">
       <c r="G11" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AQ11" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="12" spans="7:43">
       <c r="G12" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AQ12" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="13" spans="7:43">
       <c r="G13" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AQ13" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="14" spans="7:43">
       <c r="G14" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AQ14" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="15" spans="7:43">
       <c r="G15" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AQ15" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="16" spans="7:43">
       <c r="G16" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AQ16" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="17" spans="7:43">
       <c r="G17" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AQ17" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="18" spans="7:43">
       <c r="G18" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AQ18" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="19" spans="7:43">
       <c r="G19" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AQ19" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="20" spans="7:43">
       <c r="G20" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AQ20" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="21" spans="7:43">
       <c r="G21" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AQ21" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="22" spans="7:43">
       <c r="G22" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AQ22" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="23" spans="7:43">
       <c r="G23" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AQ23" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="24" spans="7:43">
       <c r="G24" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AQ24" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="25" spans="7:43">
       <c r="G25" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AQ25" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="26" spans="7:43">
       <c r="G26" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AQ26" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="27" spans="7:43">
       <c r="G27" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AQ27" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="28" spans="7:43">
       <c r="G28" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AQ28" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="29" spans="7:43">
       <c r="G29" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AQ29" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="30" spans="7:43">
       <c r="G30" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AQ30" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="31" spans="7:43">
       <c r="AQ31" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="32" spans="7:43">
       <c r="AQ32" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="33" spans="43:43">
       <c r="AQ33" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="34" spans="43:43">
       <c r="AQ34" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="35" spans="43:43">
       <c r="AQ35" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="36" spans="43:43">
       <c r="AQ36" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="37" spans="43:43">
       <c r="AQ37" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="38" spans="43:43">
       <c r="AQ38" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="39" spans="43:43">
       <c r="AQ39" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="40" spans="43:43">
       <c r="AQ40" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="41" spans="43:43">
       <c r="AQ41" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="42" spans="43:43">
       <c r="AQ42" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="43" spans="43:43">
       <c r="AQ43" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="44" spans="43:43">
       <c r="AQ44" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="45" spans="43:43">
       <c r="AQ45" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="46" spans="43:43">
       <c r="AQ46" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="47" spans="43:43">
       <c r="AQ47" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="48" spans="43:43">
       <c r="AQ48" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="49" spans="43:43">
       <c r="AQ49" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="50" spans="43:43">
       <c r="AQ50" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="51" spans="43:43">
       <c r="AQ51" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="52" spans="43:43">
       <c r="AQ52" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="53" spans="43:43">
       <c r="AQ53" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="54" spans="43:43">
       <c r="AQ54" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="55" spans="43:43">
       <c r="AQ55" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="56" spans="43:43">
       <c r="AQ56" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="57" spans="43:43">
       <c r="AQ57" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="58" spans="43:43">
       <c r="AQ58" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="59" spans="43:43">
       <c r="AQ59" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="60" spans="43:43">
       <c r="AQ60" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="61" spans="43:43">
       <c r="AQ61" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="62" spans="43:43">
       <c r="AQ62" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="63" spans="43:43">
       <c r="AQ63" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="64" spans="43:43">
       <c r="AQ64" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="65" spans="43:43">
       <c r="AQ65" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="66" spans="43:43">
       <c r="AQ66" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="67" spans="43:43">
       <c r="AQ67" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="68" spans="43:43">
       <c r="AQ68" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="69" spans="43:43">
       <c r="AQ69" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="70" spans="43:43">
       <c r="AQ70" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="71" spans="43:43">
       <c r="AQ71" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="72" spans="43:43">
       <c r="AQ72" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="73" spans="43:43">
       <c r="AQ73" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="74" spans="43:43">
       <c r="AQ74" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="75" spans="43:43">
       <c r="AQ75" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="76" spans="43:43">
       <c r="AQ76" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="77" spans="43:43">
       <c r="AQ77" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="78" spans="43:43">
       <c r="AQ78" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="79" spans="43:43">
       <c r="AQ79" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="80" spans="43:43">
       <c r="AQ80" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="81" spans="43:43">
       <c r="AQ81" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="82" spans="43:43">
       <c r="AQ82" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="83" spans="43:43">
       <c r="AQ83" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="84" spans="43:43">
       <c r="AQ84" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="85" spans="43:43">
       <c r="AQ85" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="86" spans="43:43">
       <c r="AQ86" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="87" spans="43:43">
       <c r="AQ87" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="88" spans="43:43">
       <c r="AQ88" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="89" spans="43:43">
       <c r="AQ89" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="90" spans="43:43">
       <c r="AQ90" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="91" spans="43:43">
       <c r="AQ91" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="92" spans="43:43">
       <c r="AQ92" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="93" spans="43:43">
       <c r="AQ93" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="94" spans="43:43">
       <c r="AQ94" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="95" spans="43:43">
       <c r="AQ95" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="96" spans="43:43">
       <c r="AQ96" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="97" spans="43:43">
       <c r="AQ97" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="98" spans="43:43">
       <c r="AQ98" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="99" spans="43:43">
       <c r="AQ99" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="100" spans="43:43">
       <c r="AQ100" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="101" spans="43:43">
       <c r="AQ101" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="102" spans="43:43">
       <c r="AQ102" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="103" spans="43:43">
       <c r="AQ103" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="104" spans="43:43">
       <c r="AQ104" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="105" spans="43:43">
       <c r="AQ105" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="106" spans="43:43">
       <c r="AQ106" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="107" spans="43:43">
       <c r="AQ107" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="108" spans="43:43">
       <c r="AQ108" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="109" spans="43:43">
       <c r="AQ109" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="110" spans="43:43">
       <c r="AQ110" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="111" spans="43:43">
       <c r="AQ111" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="112" spans="43:43">
       <c r="AQ112" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="113" spans="43:43">
       <c r="AQ113" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="114" spans="43:43">
       <c r="AQ114" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="115" spans="43:43">
       <c r="AQ115" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="116" spans="43:43">
       <c r="AQ116" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="117" spans="43:43">
       <c r="AQ117" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="118" spans="43:43">
       <c r="AQ118" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="119" spans="43:43">
       <c r="AQ119" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="120" spans="43:43">
       <c r="AQ120" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="121" spans="43:43">
       <c r="AQ121" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="122" spans="43:43">
       <c r="AQ122" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="123" spans="43:43">
       <c r="AQ123" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="124" spans="43:43">
       <c r="AQ124" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="125" spans="43:43">
       <c r="AQ125" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="126" spans="43:43">
       <c r="AQ126" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="127" spans="43:43">
       <c r="AQ127" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="128" spans="43:43">
       <c r="AQ128" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="129" spans="43:43">
       <c r="AQ129" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="130" spans="43:43">
       <c r="AQ130" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="131" spans="43:43">
       <c r="AQ131" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="132" spans="43:43">
       <c r="AQ132" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="133" spans="43:43">
       <c r="AQ133" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="134" spans="43:43">
       <c r="AQ134" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="135" spans="43:43">
       <c r="AQ135" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="136" spans="43:43">
       <c r="AQ136" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="137" spans="43:43">
       <c r="AQ137" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="138" spans="43:43">
       <c r="AQ138" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="139" spans="43:43">
       <c r="AQ139" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="140" spans="43:43">
       <c r="AQ140" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="141" spans="43:43">
       <c r="AQ141" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="142" spans="43:43">
       <c r="AQ142" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="143" spans="43:43">
       <c r="AQ143" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="144" spans="43:43">
       <c r="AQ144" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="145" spans="43:43">
       <c r="AQ145" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="146" spans="43:43">
       <c r="AQ146" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="147" spans="43:43">
       <c r="AQ147" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="148" spans="43:43">
       <c r="AQ148" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="149" spans="43:43">
       <c r="AQ149" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="150" spans="43:43">
       <c r="AQ150" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="151" spans="43:43">
       <c r="AQ151" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="152" spans="43:43">
       <c r="AQ152" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="153" spans="43:43">
       <c r="AQ153" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="154" spans="43:43">
       <c r="AQ154" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="155" spans="43:43">
       <c r="AQ155" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="156" spans="43:43">
       <c r="AQ156" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="157" spans="43:43">
       <c r="AQ157" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="158" spans="43:43">
       <c r="AQ158" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="159" spans="43:43">
       <c r="AQ159" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="160" spans="43:43">
       <c r="AQ160" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="161" spans="43:43">
       <c r="AQ161" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="162" spans="43:43">
       <c r="AQ162" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="163" spans="43:43">
       <c r="AQ163" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="164" spans="43:43">
       <c r="AQ164" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="165" spans="43:43">
       <c r="AQ165" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="166" spans="43:43">
       <c r="AQ166" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="167" spans="43:43">
       <c r="AQ167" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="168" spans="43:43">
       <c r="AQ168" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="169" spans="43:43">
       <c r="AQ169" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="170" spans="43:43">
       <c r="AQ170" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="171" spans="43:43">
       <c r="AQ171" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="172" spans="43:43">
       <c r="AQ172" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="173" spans="43:43">
       <c r="AQ173" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="174" spans="43:43">
       <c r="AQ174" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="175" spans="43:43">
       <c r="AQ175" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="176" spans="43:43">
       <c r="AQ176" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="177" spans="43:43">
       <c r="AQ177" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="178" spans="43:43">
       <c r="AQ178" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="179" spans="43:43">
       <c r="AQ179" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="180" spans="43:43">
       <c r="AQ180" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="181" spans="43:43">
       <c r="AQ181" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="182" spans="43:43">
       <c r="AQ182" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="183" spans="43:43">
       <c r="AQ183" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="184" spans="43:43">
       <c r="AQ184" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="185" spans="43:43">
       <c r="AQ185" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="186" spans="43:43">
       <c r="AQ186" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="187" spans="43:43">
       <c r="AQ187" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="188" spans="43:43">
       <c r="AQ188" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="189" spans="43:43">
       <c r="AQ189" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="190" spans="43:43">
       <c r="AQ190" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="191" spans="43:43">
       <c r="AQ191" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="192" spans="43:43">
       <c r="AQ192" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="193" spans="43:43">
       <c r="AQ193" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="194" spans="43:43">
       <c r="AQ194" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="195" spans="43:43">
       <c r="AQ195" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="196" spans="43:43">
       <c r="AQ196" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="197" spans="43:43">
       <c r="AQ197" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="198" spans="43:43">
       <c r="AQ198" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="199" spans="43:43">
       <c r="AQ199" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="200" spans="43:43">
       <c r="AQ200" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="201" spans="43:43">
       <c r="AQ201" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="202" spans="43:43">
       <c r="AQ202" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="203" spans="43:43">
       <c r="AQ203" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="204" spans="43:43">
       <c r="AQ204" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="205" spans="43:43">
       <c r="AQ205" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="206" spans="43:43">
       <c r="AQ206" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="207" spans="43:43">
       <c r="AQ207" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="208" spans="43:43">
       <c r="AQ208" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="209" spans="43:43">
       <c r="AQ209" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="210" spans="43:43">
       <c r="AQ210" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="211" spans="43:43">
       <c r="AQ211" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="212" spans="43:43">
       <c r="AQ212" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="213" spans="43:43">
       <c r="AQ213" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="214" spans="43:43">
       <c r="AQ214" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="215" spans="43:43">
       <c r="AQ215" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="216" spans="43:43">
       <c r="AQ216" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="217" spans="43:43">
       <c r="AQ217" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="218" spans="43:43">
       <c r="AQ218" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="219" spans="43:43">
       <c r="AQ219" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="220" spans="43:43">
       <c r="AQ220" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="221" spans="43:43">
       <c r="AQ221" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="222" spans="43:43">
       <c r="AQ222" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="223" spans="43:43">
       <c r="AQ223" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="224" spans="43:43">
       <c r="AQ224" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="225" spans="43:43">
       <c r="AQ225" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="226" spans="43:43">
       <c r="AQ226" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="227" spans="43:43">
       <c r="AQ227" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="228" spans="43:43">
       <c r="AQ228" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="229" spans="43:43">
       <c r="AQ229" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="230" spans="43:43">
       <c r="AQ230" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="231" spans="43:43">
       <c r="AQ231" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="232" spans="43:43">
       <c r="AQ232" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="233" spans="43:43">
       <c r="AQ233" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="234" spans="43:43">
       <c r="AQ234" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="235" spans="43:43">
       <c r="AQ235" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="236" spans="43:43">
       <c r="AQ236" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="237" spans="43:43">
       <c r="AQ237" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="238" spans="43:43">
       <c r="AQ238" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="239" spans="43:43">
       <c r="AQ239" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="240" spans="43:43">
       <c r="AQ240" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="241" spans="43:43">
       <c r="AQ241" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="242" spans="43:43">
       <c r="AQ242" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="243" spans="43:43">
       <c r="AQ243" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="244" spans="43:43">
       <c r="AQ244" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="245" spans="43:43">
       <c r="AQ245" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="246" spans="43:43">
       <c r="AQ246" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="247" spans="43:43">
       <c r="AQ247" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="248" spans="43:43">
       <c r="AQ248" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="249" spans="43:43">
       <c r="AQ249" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="250" spans="43:43">
       <c r="AQ250" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="251" spans="43:43">
       <c r="AQ251" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="252" spans="43:43">
       <c r="AQ252" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="253" spans="43:43">
       <c r="AQ253" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="254" spans="43:43">
       <c r="AQ254" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="255" spans="43:43">
       <c r="AQ255" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="256" spans="43:43">
       <c r="AQ256" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="257" spans="43:43">
       <c r="AQ257" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="258" spans="43:43">
       <c r="AQ258" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="259" spans="43:43">
       <c r="AQ259" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="260" spans="43:43">
       <c r="AQ260" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="261" spans="43:43">
       <c r="AQ261" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="262" spans="43:43">
       <c r="AQ262" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="263" spans="43:43">
       <c r="AQ263" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="264" spans="43:43">
       <c r="AQ264" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="265" spans="43:43">
       <c r="AQ265" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="266" spans="43:43">
       <c r="AQ266" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="267" spans="43:43">
       <c r="AQ267" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="268" spans="43:43">
       <c r="AQ268" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="269" spans="43:43">
       <c r="AQ269" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="270" spans="43:43">
       <c r="AQ270" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="271" spans="43:43">
       <c r="AQ271" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="272" spans="43:43">
       <c r="AQ272" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="273" spans="43:43">
       <c r="AQ273" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="274" spans="43:43">
       <c r="AQ274" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="275" spans="43:43">
       <c r="AQ275" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="276" spans="43:43">
       <c r="AQ276" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="277" spans="43:43">
       <c r="AQ277" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="278" spans="43:43">
       <c r="AQ278" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="279" spans="43:43">
       <c r="AQ279" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="280" spans="43:43">
       <c r="AQ280" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="281" spans="43:43">
       <c r="AQ281" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="282" spans="43:43">
       <c r="AQ282" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="283" spans="43:43">
       <c r="AQ283" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="284" spans="43:43">
       <c r="AQ284" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="285" spans="43:43">
       <c r="AQ285" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="286" spans="43:43">
       <c r="AQ286" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="287" spans="43:43">
       <c r="AQ287" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="288" spans="43:43">
       <c r="AQ288" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="289" spans="43:43">
       <c r="AQ289" t="s">
-        <v>681</v>
+        <v>683</v>
+      </c>
+    </row>
+    <row r="290" spans="43:43">
+      <c r="AQ290" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="291" spans="43:43">
+      <c r="AQ291" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="292" spans="43:43">
+      <c r="AQ292" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="293" spans="43:43">
+      <c r="AQ293" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="294" spans="43:43">
+      <c r="AQ294" t="s">
+        <v>688</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000025/metadata_template_ERC000025.xlsx
+++ b/templates/ERC000025/metadata_template_ERC000025.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
     <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AQ$1:$AQ$294</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$89</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="805">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="806">
   <si>
     <t>alias</t>
   </si>
@@ -732,6 +732,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>UG 200</t>
   </si>
   <si>
     <t>Vega</t>
@@ -2980,7 +2983,7 @@
         <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3024,7 +3027,7 @@
         <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -3051,7 +3054,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N88"/>
+  <dimension ref="G1:N89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3788,6 +3791,11 @@
     </row>
     <row r="88" spans="14:14">
       <c r="N88" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="89" spans="14:14">
+      <c r="N89" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3809,27 +3817,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -3849,122 +3857,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -3988,600 +3996,600 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="2" spans="1:100" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
   </sheetData>
@@ -4616,1613 +4624,1613 @@
   <sheetData>
     <row r="1" spans="7:43">
       <c r="G1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Z1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AQ1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2" spans="7:43">
       <c r="G2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Z2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AQ2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="3" spans="7:43">
       <c r="G3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Z3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AQ3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="4" spans="7:43">
       <c r="G4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AQ4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5" spans="7:43">
       <c r="G5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AQ5" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6" spans="7:43">
       <c r="G6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AQ6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" spans="7:43">
       <c r="G7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AQ7" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="7:43">
       <c r="G8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AQ8" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9" spans="7:43">
       <c r="G9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AQ9" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="10" spans="7:43">
       <c r="G10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AQ10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="11" spans="7:43">
       <c r="G11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AQ11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="12" spans="7:43">
       <c r="G12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AQ12" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="13" spans="7:43">
       <c r="G13" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AQ13" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="14" spans="7:43">
       <c r="G14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AQ14" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="15" spans="7:43">
       <c r="G15" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AQ15" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="16" spans="7:43">
       <c r="G16" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AQ16" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="17" spans="7:43">
       <c r="G17" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AQ17" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="18" spans="7:43">
       <c r="G18" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AQ18" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="19" spans="7:43">
       <c r="G19" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AQ19" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="20" spans="7:43">
       <c r="G20" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AQ20" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="21" spans="7:43">
       <c r="G21" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AQ21" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="22" spans="7:43">
       <c r="G22" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AQ22" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="23" spans="7:43">
       <c r="G23" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AQ23" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="24" spans="7:43">
       <c r="G24" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AQ24" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="25" spans="7:43">
       <c r="G25" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AQ25" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="26" spans="7:43">
       <c r="G26" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AQ26" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="27" spans="7:43">
       <c r="G27" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AQ27" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="28" spans="7:43">
       <c r="G28" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AQ28" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="29" spans="7:43">
       <c r="G29" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AQ29" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="30" spans="7:43">
       <c r="G30" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AQ30" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="31" spans="7:43">
       <c r="AQ31" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="32" spans="7:43">
       <c r="AQ32" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="33" spans="43:43">
       <c r="AQ33" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="34" spans="43:43">
       <c r="AQ34" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="35" spans="43:43">
       <c r="AQ35" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="36" spans="43:43">
       <c r="AQ36" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="37" spans="43:43">
       <c r="AQ37" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="38" spans="43:43">
       <c r="AQ38" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="39" spans="43:43">
       <c r="AQ39" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="40" spans="43:43">
       <c r="AQ40" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="41" spans="43:43">
       <c r="AQ41" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="42" spans="43:43">
       <c r="AQ42" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="43" spans="43:43">
       <c r="AQ43" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="44" spans="43:43">
       <c r="AQ44" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="45" spans="43:43">
       <c r="AQ45" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="46" spans="43:43">
       <c r="AQ46" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="47" spans="43:43">
       <c r="AQ47" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="48" spans="43:43">
       <c r="AQ48" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="49" spans="43:43">
       <c r="AQ49" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="50" spans="43:43">
       <c r="AQ50" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="51" spans="43:43">
       <c r="AQ51" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="52" spans="43:43">
       <c r="AQ52" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="53" spans="43:43">
       <c r="AQ53" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="54" spans="43:43">
       <c r="AQ54" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="55" spans="43:43">
       <c r="AQ55" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="56" spans="43:43">
       <c r="AQ56" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="57" spans="43:43">
       <c r="AQ57" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="58" spans="43:43">
       <c r="AQ58" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="59" spans="43:43">
       <c r="AQ59" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="60" spans="43:43">
       <c r="AQ60" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="61" spans="43:43">
       <c r="AQ61" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="62" spans="43:43">
       <c r="AQ62" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="63" spans="43:43">
       <c r="AQ63" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="64" spans="43:43">
       <c r="AQ64" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="65" spans="43:43">
       <c r="AQ65" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="66" spans="43:43">
       <c r="AQ66" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="67" spans="43:43">
       <c r="AQ67" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="68" spans="43:43">
       <c r="AQ68" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="69" spans="43:43">
       <c r="AQ69" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="70" spans="43:43">
       <c r="AQ70" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="71" spans="43:43">
       <c r="AQ71" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="72" spans="43:43">
       <c r="AQ72" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="73" spans="43:43">
       <c r="AQ73" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="74" spans="43:43">
       <c r="AQ74" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="75" spans="43:43">
       <c r="AQ75" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="76" spans="43:43">
       <c r="AQ76" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="77" spans="43:43">
       <c r="AQ77" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="78" spans="43:43">
       <c r="AQ78" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="79" spans="43:43">
       <c r="AQ79" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="80" spans="43:43">
       <c r="AQ80" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="81" spans="43:43">
       <c r="AQ81" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="82" spans="43:43">
       <c r="AQ82" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="83" spans="43:43">
       <c r="AQ83" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="84" spans="43:43">
       <c r="AQ84" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="85" spans="43:43">
       <c r="AQ85" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="86" spans="43:43">
       <c r="AQ86" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="87" spans="43:43">
       <c r="AQ87" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="88" spans="43:43">
       <c r="AQ88" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="89" spans="43:43">
       <c r="AQ89" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="90" spans="43:43">
       <c r="AQ90" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="91" spans="43:43">
       <c r="AQ91" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="92" spans="43:43">
       <c r="AQ92" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="93" spans="43:43">
       <c r="AQ93" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="94" spans="43:43">
       <c r="AQ94" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="95" spans="43:43">
       <c r="AQ95" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="96" spans="43:43">
       <c r="AQ96" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="97" spans="43:43">
       <c r="AQ97" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="98" spans="43:43">
       <c r="AQ98" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="99" spans="43:43">
       <c r="AQ99" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="100" spans="43:43">
       <c r="AQ100" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="101" spans="43:43">
       <c r="AQ101" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="102" spans="43:43">
       <c r="AQ102" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="103" spans="43:43">
       <c r="AQ103" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="104" spans="43:43">
       <c r="AQ104" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="105" spans="43:43">
       <c r="AQ105" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="106" spans="43:43">
       <c r="AQ106" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="107" spans="43:43">
       <c r="AQ107" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="108" spans="43:43">
       <c r="AQ108" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="109" spans="43:43">
       <c r="AQ109" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="110" spans="43:43">
       <c r="AQ110" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="111" spans="43:43">
       <c r="AQ111" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="112" spans="43:43">
       <c r="AQ112" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="113" spans="43:43">
       <c r="AQ113" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="114" spans="43:43">
       <c r="AQ114" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="115" spans="43:43">
       <c r="AQ115" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="116" spans="43:43">
       <c r="AQ116" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="117" spans="43:43">
       <c r="AQ117" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="118" spans="43:43">
       <c r="AQ118" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="119" spans="43:43">
       <c r="AQ119" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="120" spans="43:43">
       <c r="AQ120" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="121" spans="43:43">
       <c r="AQ121" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="122" spans="43:43">
       <c r="AQ122" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="123" spans="43:43">
       <c r="AQ123" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="124" spans="43:43">
       <c r="AQ124" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="125" spans="43:43">
       <c r="AQ125" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="126" spans="43:43">
       <c r="AQ126" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="127" spans="43:43">
       <c r="AQ127" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="128" spans="43:43">
       <c r="AQ128" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="129" spans="43:43">
       <c r="AQ129" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="130" spans="43:43">
       <c r="AQ130" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="131" spans="43:43">
       <c r="AQ131" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="132" spans="43:43">
       <c r="AQ132" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="133" spans="43:43">
       <c r="AQ133" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="134" spans="43:43">
       <c r="AQ134" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="135" spans="43:43">
       <c r="AQ135" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="136" spans="43:43">
       <c r="AQ136" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="137" spans="43:43">
       <c r="AQ137" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="138" spans="43:43">
       <c r="AQ138" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="139" spans="43:43">
       <c r="AQ139" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="140" spans="43:43">
       <c r="AQ140" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="141" spans="43:43">
       <c r="AQ141" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="142" spans="43:43">
       <c r="AQ142" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="143" spans="43:43">
       <c r="AQ143" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="144" spans="43:43">
       <c r="AQ144" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="145" spans="43:43">
       <c r="AQ145" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="146" spans="43:43">
       <c r="AQ146" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="147" spans="43:43">
       <c r="AQ147" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="148" spans="43:43">
       <c r="AQ148" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="149" spans="43:43">
       <c r="AQ149" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="150" spans="43:43">
       <c r="AQ150" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="151" spans="43:43">
       <c r="AQ151" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="152" spans="43:43">
       <c r="AQ152" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="153" spans="43:43">
       <c r="AQ153" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="154" spans="43:43">
       <c r="AQ154" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="155" spans="43:43">
       <c r="AQ155" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="156" spans="43:43">
       <c r="AQ156" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="157" spans="43:43">
       <c r="AQ157" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="158" spans="43:43">
       <c r="AQ158" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="159" spans="43:43">
       <c r="AQ159" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="160" spans="43:43">
       <c r="AQ160" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="161" spans="43:43">
       <c r="AQ161" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="162" spans="43:43">
       <c r="AQ162" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="163" spans="43:43">
       <c r="AQ163" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="164" spans="43:43">
       <c r="AQ164" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="165" spans="43:43">
       <c r="AQ165" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="166" spans="43:43">
       <c r="AQ166" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="167" spans="43:43">
       <c r="AQ167" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="168" spans="43:43">
       <c r="AQ168" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="169" spans="43:43">
       <c r="AQ169" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="170" spans="43:43">
       <c r="AQ170" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="171" spans="43:43">
       <c r="AQ171" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="172" spans="43:43">
       <c r="AQ172" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="173" spans="43:43">
       <c r="AQ173" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="174" spans="43:43">
       <c r="AQ174" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="175" spans="43:43">
       <c r="AQ175" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="176" spans="43:43">
       <c r="AQ176" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="177" spans="43:43">
       <c r="AQ177" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="178" spans="43:43">
       <c r="AQ178" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="179" spans="43:43">
       <c r="AQ179" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="180" spans="43:43">
       <c r="AQ180" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="181" spans="43:43">
       <c r="AQ181" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="182" spans="43:43">
       <c r="AQ182" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="183" spans="43:43">
       <c r="AQ183" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="184" spans="43:43">
       <c r="AQ184" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="185" spans="43:43">
       <c r="AQ185" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="186" spans="43:43">
       <c r="AQ186" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="187" spans="43:43">
       <c r="AQ187" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="188" spans="43:43">
       <c r="AQ188" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="189" spans="43:43">
       <c r="AQ189" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="190" spans="43:43">
       <c r="AQ190" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="191" spans="43:43">
       <c r="AQ191" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="192" spans="43:43">
       <c r="AQ192" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="193" spans="43:43">
       <c r="AQ193" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="194" spans="43:43">
       <c r="AQ194" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="195" spans="43:43">
       <c r="AQ195" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="196" spans="43:43">
       <c r="AQ196" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="197" spans="43:43">
       <c r="AQ197" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="198" spans="43:43">
       <c r="AQ198" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="199" spans="43:43">
       <c r="AQ199" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="200" spans="43:43">
       <c r="AQ200" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="201" spans="43:43">
       <c r="AQ201" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="202" spans="43:43">
       <c r="AQ202" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="203" spans="43:43">
       <c r="AQ203" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="204" spans="43:43">
       <c r="AQ204" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="205" spans="43:43">
       <c r="AQ205" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="206" spans="43:43">
       <c r="AQ206" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="207" spans="43:43">
       <c r="AQ207" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="208" spans="43:43">
       <c r="AQ208" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="209" spans="43:43">
       <c r="AQ209" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="210" spans="43:43">
       <c r="AQ210" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="211" spans="43:43">
       <c r="AQ211" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="212" spans="43:43">
       <c r="AQ212" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="213" spans="43:43">
       <c r="AQ213" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="214" spans="43:43">
       <c r="AQ214" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="215" spans="43:43">
       <c r="AQ215" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="216" spans="43:43">
       <c r="AQ216" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="217" spans="43:43">
       <c r="AQ217" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="218" spans="43:43">
       <c r="AQ218" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="219" spans="43:43">
       <c r="AQ219" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="220" spans="43:43">
       <c r="AQ220" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="221" spans="43:43">
       <c r="AQ221" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="222" spans="43:43">
       <c r="AQ222" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="223" spans="43:43">
       <c r="AQ223" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="224" spans="43:43">
       <c r="AQ224" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="225" spans="43:43">
       <c r="AQ225" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="226" spans="43:43">
       <c r="AQ226" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="227" spans="43:43">
       <c r="AQ227" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="228" spans="43:43">
       <c r="AQ228" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="229" spans="43:43">
       <c r="AQ229" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="230" spans="43:43">
       <c r="AQ230" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="231" spans="43:43">
       <c r="AQ231" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="232" spans="43:43">
       <c r="AQ232" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="233" spans="43:43">
       <c r="AQ233" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="234" spans="43:43">
       <c r="AQ234" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="235" spans="43:43">
       <c r="AQ235" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="236" spans="43:43">
       <c r="AQ236" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="237" spans="43:43">
       <c r="AQ237" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="238" spans="43:43">
       <c r="AQ238" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="239" spans="43:43">
       <c r="AQ239" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="240" spans="43:43">
       <c r="AQ240" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="241" spans="43:43">
       <c r="AQ241" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="242" spans="43:43">
       <c r="AQ242" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="243" spans="43:43">
       <c r="AQ243" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="244" spans="43:43">
       <c r="AQ244" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="245" spans="43:43">
       <c r="AQ245" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="246" spans="43:43">
       <c r="AQ246" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="247" spans="43:43">
       <c r="AQ247" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="248" spans="43:43">
       <c r="AQ248" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="249" spans="43:43">
       <c r="AQ249" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="250" spans="43:43">
       <c r="AQ250" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="251" spans="43:43">
       <c r="AQ251" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="252" spans="43:43">
       <c r="AQ252" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="253" spans="43:43">
       <c r="AQ253" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="254" spans="43:43">
       <c r="AQ254" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="255" spans="43:43">
       <c r="AQ255" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="256" spans="43:43">
       <c r="AQ256" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="257" spans="43:43">
       <c r="AQ257" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="258" spans="43:43">
       <c r="AQ258" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="259" spans="43:43">
       <c r="AQ259" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="260" spans="43:43">
       <c r="AQ260" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="261" spans="43:43">
       <c r="AQ261" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="262" spans="43:43">
       <c r="AQ262" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="263" spans="43:43">
       <c r="AQ263" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="264" spans="43:43">
       <c r="AQ264" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="265" spans="43:43">
       <c r="AQ265" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="266" spans="43:43">
       <c r="AQ266" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="267" spans="43:43">
       <c r="AQ267" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="268" spans="43:43">
       <c r="AQ268" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="269" spans="43:43">
       <c r="AQ269" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="270" spans="43:43">
       <c r="AQ270" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="271" spans="43:43">
       <c r="AQ271" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="272" spans="43:43">
       <c r="AQ272" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="273" spans="43:43">
       <c r="AQ273" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="274" spans="43:43">
       <c r="AQ274" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="275" spans="43:43">
       <c r="AQ275" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="276" spans="43:43">
       <c r="AQ276" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="277" spans="43:43">
       <c r="AQ277" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="278" spans="43:43">
       <c r="AQ278" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="279" spans="43:43">
       <c r="AQ279" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="280" spans="43:43">
       <c r="AQ280" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="281" spans="43:43">
       <c r="AQ281" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="282" spans="43:43">
       <c r="AQ282" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="283" spans="43:43">
       <c r="AQ283" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="284" spans="43:43">
       <c r="AQ284" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="285" spans="43:43">
       <c r="AQ285" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="286" spans="43:43">
       <c r="AQ286" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="287" spans="43:43">
       <c r="AQ287" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="288" spans="43:43">
       <c r="AQ288" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="289" spans="43:43">
       <c r="AQ289" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="290" spans="43:43">
       <c r="AQ290" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="291" spans="43:43">
       <c r="AQ291" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="292" spans="43:43">
       <c r="AQ292" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="293" spans="43:43">
       <c r="AQ293" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="294" spans="43:43">
       <c r="AQ294" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
   </sheetData>
